--- a/georgia-county-indicators.xlsx
+++ b/georgia-county-indicators.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/colinhvu/Documents/coding/factxis/percentile-based-viz/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coduser\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3F72D6-78B4-E442-B5C8-60D664ED2F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D64B3A-414C-4461-99FF-B35CB6684F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1254" yWindow="930" windowWidth="21786" windowHeight="12030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="us-county-indicators" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="173">
   <si>
     <t>FIPS_Code</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>Life Expectancy</t>
-  </si>
-  <si>
-    <t>Incarceration Rate</t>
   </si>
   <si>
     <t>Incarceration_Rate_1k</t>
@@ -976,8 +973,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M160"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:L160"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.6640625" customWidth="1"/>
@@ -985,16 +982,15 @@
     <col min="4" max="4" width="22.33203125" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" customWidth="1"/>
-    <col min="10" max="10" width="22.33203125" customWidth="1"/>
-    <col min="11" max="11" width="29.5" customWidth="1"/>
-    <col min="12" max="12" width="26.33203125" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" customWidth="1"/>
+    <col min="10" max="10" width="29.5" customWidth="1"/>
+    <col min="11" max="11" width="26.33203125" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1031,183 +1027,168 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>13001</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2">
         <v>36.1</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>74.553535310000001</v>
       </c>
       <c r="G2">
-        <v>504.8</v>
+        <v>5.05</v>
       </c>
       <c r="H2">
-        <v>5.05</v>
-      </c>
-      <c r="I2">
         <v>0.2</v>
       </c>
-      <c r="J2" t="s">
-        <v>14</v>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2">
+        <v>74.900000000000006</v>
       </c>
       <c r="K2">
-        <v>74.900000000000006</v>
+        <v>0.45860000000000001</v>
       </c>
       <c r="L2">
-        <v>0.45860000000000001</v>
-      </c>
-      <c r="M2">
         <v>36.28</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>13003</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>32.1</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>73.462140340000005</v>
       </c>
       <c r="G3">
-        <v>611.22</v>
+        <v>6.11</v>
       </c>
       <c r="H3">
-        <v>6.11</v>
-      </c>
-      <c r="I3">
         <v>0.3</v>
       </c>
-      <c r="J3" t="s">
-        <v>14</v>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>67.2</v>
       </c>
       <c r="K3">
-        <v>67.2</v>
+        <v>0.47349999999999998</v>
       </c>
       <c r="L3">
-        <v>0.47349999999999998</v>
-      </c>
-      <c r="M3">
         <v>24.04</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>13005</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4">
         <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4">
         <v>72.577063480000007</v>
       </c>
       <c r="G4">
-        <v>720.51</v>
+        <v>7.21</v>
       </c>
       <c r="H4">
-        <v>7.21</v>
-      </c>
-      <c r="I4">
         <v>0.5</v>
       </c>
-      <c r="J4" t="s">
-        <v>14</v>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <v>82.1</v>
       </c>
       <c r="K4">
-        <v>82.1</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="L4">
-        <v>0.46200000000000002</v>
-      </c>
-      <c r="M4">
         <v>39.43</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>13007</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5">
         <v>32.5</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>76.226225679999999</v>
       </c>
       <c r="G5">
-        <v>250.31</v>
+        <v>2.5</v>
       </c>
       <c r="H5">
-        <v>2.5</v>
-      </c>
-      <c r="I5">
         <v>0.3</v>
       </c>
-      <c r="J5" t="s">
-        <v>14</v>
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>80.599999999999994</v>
       </c>
       <c r="K5">
-        <v>80.599999999999994</v>
+        <v>0.4874</v>
       </c>
       <c r="L5">
-        <v>0.4874</v>
-      </c>
-      <c r="M5">
         <v>9.16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>13009</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6">
         <v>34.1</v>
@@ -1219,77 +1200,71 @@
         <v>75.244220560000002</v>
       </c>
       <c r="G6">
-        <v>663.12</v>
+        <v>6.63</v>
       </c>
       <c r="H6">
-        <v>6.63</v>
-      </c>
-      <c r="I6">
         <v>0.3</v>
       </c>
-      <c r="J6" t="s">
-        <v>14</v>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>85.8</v>
       </c>
       <c r="K6">
-        <v>85.8</v>
+        <v>0.46389999999999998</v>
       </c>
       <c r="L6">
-        <v>0.46389999999999998</v>
-      </c>
-      <c r="M6">
         <v>174.38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>13011</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7">
         <v>31.6</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>76.073007590000003</v>
       </c>
       <c r="G7">
-        <v>348.24</v>
+        <v>3.48</v>
       </c>
       <c r="H7">
-        <v>3.48</v>
-      </c>
-      <c r="I7">
         <v>0.1</v>
       </c>
-      <c r="J7" t="s">
-        <v>14</v>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>75.900000000000006</v>
       </c>
       <c r="K7">
-        <v>75.900000000000006</v>
+        <v>0.41620000000000001</v>
       </c>
       <c r="L7">
-        <v>0.41620000000000001</v>
-      </c>
-      <c r="M7">
         <v>80.62</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>13013</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <v>35.200000000000003</v>
@@ -1301,36 +1276,33 @@
         <v>76.658556200000007</v>
       </c>
       <c r="G8">
-        <v>373.51</v>
+        <v>3.74</v>
       </c>
       <c r="H8">
-        <v>3.74</v>
+        <v>0.2</v>
       </c>
       <c r="I8">
-        <v>0.2</v>
+        <v>13.21</v>
       </c>
       <c r="J8">
-        <v>13.21</v>
+        <v>84.5</v>
       </c>
       <c r="K8">
-        <v>84.5</v>
+        <v>0.3931</v>
       </c>
       <c r="L8">
-        <v>0.3931</v>
-      </c>
-      <c r="M8">
         <v>490.52</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>13015</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9">
         <v>35</v>
@@ -1342,36 +1314,33 @@
         <v>76.950969459999996</v>
       </c>
       <c r="G9">
-        <v>676.93</v>
+        <v>6.77</v>
       </c>
       <c r="H9">
-        <v>6.77</v>
+        <v>0.2</v>
       </c>
       <c r="I9">
-        <v>0.2</v>
+        <v>11.14</v>
       </c>
       <c r="J9">
-        <v>11.14</v>
+        <v>83.6</v>
       </c>
       <c r="K9">
-        <v>83.6</v>
+        <v>0.43880000000000002</v>
       </c>
       <c r="L9">
-        <v>0.43880000000000002</v>
-      </c>
-      <c r="M9">
         <v>228.63</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>13017</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D10">
         <v>33.9</v>
@@ -1383,77 +1352,71 @@
         <v>73.326789930000004</v>
       </c>
       <c r="G10">
-        <v>1471.1</v>
+        <v>14.71</v>
       </c>
       <c r="H10">
-        <v>14.71</v>
-      </c>
-      <c r="I10">
         <v>0.1</v>
       </c>
-      <c r="J10" t="s">
-        <v>14</v>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10">
+        <v>83.5</v>
       </c>
       <c r="K10">
-        <v>83.5</v>
+        <v>0.48449999999999999</v>
       </c>
       <c r="L10">
-        <v>0.48449999999999999</v>
-      </c>
-      <c r="M10">
         <v>68.099999999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>13019</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D11">
         <v>33.799999999999997</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F11">
         <v>74.739188979999994</v>
       </c>
       <c r="G11">
-        <v>474.31</v>
+        <v>4.74</v>
       </c>
       <c r="H11">
-        <v>4.74</v>
-      </c>
-      <c r="I11">
         <v>0.3</v>
       </c>
-      <c r="J11" t="s">
-        <v>14</v>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11">
+        <v>79</v>
       </c>
       <c r="K11">
-        <v>79</v>
+        <v>0.43559999999999999</v>
       </c>
       <c r="L11">
-        <v>0.43559999999999999</v>
-      </c>
-      <c r="M11">
         <v>42.24</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>13021</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12">
         <v>35.6</v>
@@ -1465,200 +1428,185 @@
         <v>74.065883189999994</v>
       </c>
       <c r="G12">
-        <v>768.44</v>
+        <v>7.68</v>
       </c>
       <c r="H12">
-        <v>7.68</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>24.81</v>
       </c>
       <c r="J12">
-        <v>24.81</v>
+        <v>86</v>
       </c>
       <c r="K12">
-        <v>86</v>
+        <v>0.52</v>
       </c>
       <c r="L12">
-        <v>0.52</v>
-      </c>
-      <c r="M12">
         <v>614.28</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>13023</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13">
         <v>35.4</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13">
         <v>74.699605419999997</v>
       </c>
       <c r="G13">
-        <v>464.38</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="H13">
-        <v>4.6399999999999997</v>
-      </c>
-      <c r="I13">
         <v>0.4</v>
       </c>
-      <c r="J13" t="s">
-        <v>14</v>
+      <c r="I13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13">
+        <v>88.6</v>
       </c>
       <c r="K13">
-        <v>88.6</v>
+        <v>0.4415</v>
       </c>
       <c r="L13">
-        <v>0.4415</v>
-      </c>
-      <c r="M13">
         <v>59.33</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13025</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14">
         <v>31.7</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14">
         <v>74.825564040000003</v>
       </c>
       <c r="G14">
-        <v>331.23</v>
+        <v>3.31</v>
       </c>
       <c r="H14">
-        <v>3.31</v>
-      </c>
-      <c r="I14">
         <v>0.1</v>
       </c>
-      <c r="J14" t="s">
-        <v>14</v>
+      <c r="I14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14">
+        <v>78.900000000000006</v>
       </c>
       <c r="K14">
-        <v>78.900000000000006</v>
+        <v>0.43219999999999997</v>
       </c>
       <c r="L14">
-        <v>0.43219999999999997</v>
-      </c>
-      <c r="M14">
         <v>42.32</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13027</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15">
         <v>30.9</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F15">
         <v>75.326407849999995</v>
       </c>
       <c r="G15">
-        <v>459.18</v>
+        <v>4.59</v>
       </c>
       <c r="H15">
-        <v>4.59</v>
-      </c>
-      <c r="I15">
         <v>0.5</v>
       </c>
-      <c r="J15" t="s">
-        <v>14</v>
+      <c r="I15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15">
+        <v>85.1</v>
       </c>
       <c r="K15">
-        <v>85.1</v>
+        <v>0.54820000000000002</v>
       </c>
       <c r="L15">
-        <v>0.54820000000000002</v>
-      </c>
-      <c r="M15">
         <v>31.61</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>13029</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16">
         <v>32.4</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F16">
         <v>76.091081889999998</v>
       </c>
       <c r="G16">
-        <v>238.56</v>
+        <v>2.39</v>
       </c>
       <c r="H16">
-        <v>2.39</v>
+        <v>0.2</v>
       </c>
       <c r="I16">
-        <v>0.2</v>
+        <v>30.28</v>
       </c>
       <c r="J16">
-        <v>30.28</v>
+        <v>91.6</v>
       </c>
       <c r="K16">
-        <v>91.6</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="L16">
-        <v>0.42799999999999999</v>
-      </c>
-      <c r="M16">
         <v>84.71</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>13031</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17">
         <v>30.3</v>
@@ -1670,36 +1618,33 @@
         <v>76.545523939999995</v>
       </c>
       <c r="G17">
-        <v>769.63</v>
+        <v>7.7</v>
       </c>
       <c r="H17">
-        <v>7.7</v>
-      </c>
-      <c r="I17">
         <v>0.4</v>
       </c>
-      <c r="J17" t="s">
-        <v>14</v>
+      <c r="I17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17">
+        <v>87.3</v>
       </c>
       <c r="K17">
-        <v>87.3</v>
+        <v>0.46889999999999998</v>
       </c>
       <c r="L17">
-        <v>0.46889999999999998</v>
-      </c>
-      <c r="M17">
         <v>112.61</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>13033</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18">
         <v>32.700000000000003</v>
@@ -1711,118 +1656,109 @@
         <v>74.048892910000006</v>
       </c>
       <c r="G18">
-        <v>941.64</v>
+        <v>9.42</v>
       </c>
       <c r="H18">
-        <v>9.42</v>
-      </c>
-      <c r="I18">
         <v>0.5</v>
       </c>
-      <c r="J18" t="s">
-        <v>14</v>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18">
+        <v>80.099999999999994</v>
       </c>
       <c r="K18">
-        <v>80.099999999999994</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="L18">
-        <v>0.44700000000000001</v>
-      </c>
-      <c r="M18">
         <v>27.23</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>13035</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19">
         <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19">
         <v>74.710137509999996</v>
       </c>
       <c r="G19">
-        <v>523.54</v>
+        <v>5.24</v>
       </c>
       <c r="H19">
-        <v>5.24</v>
-      </c>
-      <c r="I19">
         <v>0.6</v>
       </c>
-      <c r="J19" t="s">
-        <v>14</v>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19">
+        <v>80.599999999999994</v>
       </c>
       <c r="K19">
-        <v>80.599999999999994</v>
+        <v>0.52159999999999995</v>
       </c>
       <c r="L19">
-        <v>0.52159999999999995</v>
-      </c>
-      <c r="M19">
         <v>131.13999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>13037</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D20">
         <v>30</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20">
         <v>75.086006729999994</v>
       </c>
       <c r="G20">
-        <v>459.35</v>
+        <v>4.59</v>
       </c>
       <c r="H20">
-        <v>4.59</v>
-      </c>
-      <c r="I20">
         <v>0.6</v>
       </c>
-      <c r="J20" t="s">
-        <v>14</v>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20">
+        <v>72.900000000000006</v>
       </c>
       <c r="K20">
-        <v>72.900000000000006</v>
+        <v>0.4748</v>
       </c>
       <c r="L20">
-        <v>0.4748</v>
-      </c>
-      <c r="M20">
         <v>22.7</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>13039</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D21">
         <v>31.9</v>
@@ -1834,77 +1770,71 @@
         <v>78.219261900000006</v>
       </c>
       <c r="G21">
-        <v>369.74</v>
+        <v>3.7</v>
       </c>
       <c r="H21">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="I21">
-        <v>0.2</v>
+        <v>20.12</v>
       </c>
       <c r="J21">
-        <v>20.12</v>
+        <v>91.3</v>
       </c>
       <c r="K21">
-        <v>91.3</v>
+        <v>0.45350000000000001</v>
       </c>
       <c r="L21">
-        <v>0.45350000000000001</v>
-      </c>
-      <c r="M21">
         <v>84.45</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>13043</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D22">
         <v>34.9</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F22">
         <v>71.324335520000005</v>
       </c>
       <c r="G22">
-        <v>1131.8699999999999</v>
+        <v>11.32</v>
       </c>
       <c r="H22">
-        <v>11.32</v>
-      </c>
-      <c r="I22">
         <v>0.3</v>
       </c>
-      <c r="J22" t="s">
-        <v>14</v>
+      <c r="I22" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22">
+        <v>77.3</v>
       </c>
       <c r="K22">
-        <v>77.3</v>
+        <v>0.5252</v>
       </c>
       <c r="L22">
-        <v>0.5252</v>
-      </c>
-      <c r="M22">
         <v>44.48</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>13045</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23">
         <v>35.1</v>
@@ -1916,36 +1846,33 @@
         <v>74.954383870000001</v>
       </c>
       <c r="G23">
-        <v>530.28</v>
+        <v>5.3</v>
       </c>
       <c r="H23">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="I23">
-        <v>0.3</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="J23">
-        <v>18.329999999999998</v>
+        <v>84.6</v>
       </c>
       <c r="K23">
-        <v>84.6</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="L23">
-        <v>0.42799999999999999</v>
-      </c>
-      <c r="M23">
         <v>234.82</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>13047</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D24">
         <v>34.6</v>
@@ -1957,77 +1884,71 @@
         <v>76.881436690000001</v>
       </c>
       <c r="G24">
-        <v>562.32000000000005</v>
+        <v>5.62</v>
       </c>
       <c r="H24">
-        <v>5.62</v>
-      </c>
-      <c r="I24">
         <v>0.1</v>
       </c>
-      <c r="J24" t="s">
-        <v>14</v>
+      <c r="I24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24">
+        <v>87.5</v>
       </c>
       <c r="K24">
-        <v>87.5</v>
+        <v>0.41789999999999999</v>
       </c>
       <c r="L24">
-        <v>0.41789999999999999</v>
-      </c>
-      <c r="M24">
         <v>411.32</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>13049</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D25">
         <v>33.1</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F25">
         <v>79.542920949999996</v>
       </c>
       <c r="G25">
-        <v>408.04</v>
+        <v>4.08</v>
       </c>
       <c r="H25">
-        <v>4.08</v>
-      </c>
-      <c r="I25">
         <v>0.5</v>
       </c>
-      <c r="J25" t="s">
-        <v>14</v>
+      <c r="I25" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25">
+        <v>74.099999999999994</v>
       </c>
       <c r="K25">
-        <v>74.099999999999994</v>
+        <v>0.42220000000000002</v>
       </c>
       <c r="L25">
-        <v>0.42220000000000002</v>
-      </c>
-      <c r="M25">
         <v>16.72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>13051</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D26">
         <v>30.8</v>
@@ -2039,118 +1960,109 @@
         <v>77.640442100000001</v>
       </c>
       <c r="G26">
-        <v>712.69</v>
+        <v>7.13</v>
       </c>
       <c r="H26">
-        <v>7.13</v>
+        <v>0.7</v>
       </c>
       <c r="I26">
-        <v>0.7</v>
+        <v>10.71</v>
       </c>
       <c r="J26">
-        <v>10.71</v>
+        <v>89.9</v>
       </c>
       <c r="K26">
-        <v>89.9</v>
+        <v>0.4869</v>
       </c>
       <c r="L26">
-        <v>0.4869</v>
-      </c>
-      <c r="M26">
         <v>666.09</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>13053</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D27">
         <v>27.6</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F27">
         <v>76.489668409999993</v>
       </c>
       <c r="G27">
-        <v>243.97</v>
+        <v>2.44</v>
       </c>
       <c r="H27">
-        <v>2.44</v>
-      </c>
-      <c r="I27">
         <v>0.1</v>
       </c>
-      <c r="J27" t="s">
-        <v>14</v>
+      <c r="I27" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27">
+        <v>94.3</v>
       </c>
       <c r="K27">
-        <v>94.3</v>
+        <v>0.46579999999999999</v>
       </c>
       <c r="L27">
-        <v>0.46579999999999999</v>
-      </c>
-      <c r="M27">
         <v>42.45</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>13055</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D28">
         <v>34.1</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28">
         <v>73.652709590000001</v>
       </c>
       <c r="G28">
-        <v>1152.8399999999999</v>
+        <v>11.53</v>
       </c>
       <c r="H28">
-        <v>11.53</v>
-      </c>
-      <c r="I28">
         <v>0.3</v>
       </c>
-      <c r="J28" t="s">
-        <v>14</v>
+      <c r="I28" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28">
+        <v>73.8</v>
       </c>
       <c r="K28">
-        <v>73.8</v>
+        <v>0.4476</v>
       </c>
       <c r="L28">
-        <v>0.4476</v>
-      </c>
-      <c r="M28">
         <v>79.19</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>13057</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D29">
         <v>26.3</v>
@@ -2162,36 +2074,33 @@
         <v>79.931669880000001</v>
       </c>
       <c r="G29">
-        <v>246.83</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="H29">
-        <v>2.4700000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="I29">
-        <v>0.2</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="J29">
-        <v>8.1199999999999992</v>
+        <v>92.1</v>
       </c>
       <c r="K29">
-        <v>92.1</v>
+        <v>0.4078</v>
       </c>
       <c r="L29">
-        <v>0.4078</v>
-      </c>
-      <c r="M29">
         <v>587.80999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>13059</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D30">
         <v>25.4</v>
@@ -2203,77 +2112,71 @@
         <v>78.577838940000007</v>
       </c>
       <c r="G30">
-        <v>389.31</v>
+        <v>3.89</v>
       </c>
       <c r="H30">
-        <v>3.89</v>
+        <v>0.4</v>
       </c>
       <c r="I30">
-        <v>0.4</v>
+        <v>10.91</v>
       </c>
       <c r="J30">
-        <v>10.91</v>
+        <v>88</v>
       </c>
       <c r="K30">
-        <v>88</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="L30">
-        <v>0.52200000000000002</v>
-      </c>
-      <c r="M30">
         <v>1058.32</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>13061</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D31">
         <v>32.6</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F31">
         <v>75.433296440000007</v>
       </c>
       <c r="G31">
-        <v>877.48</v>
+        <v>8.77</v>
       </c>
       <c r="H31">
-        <v>8.77</v>
-      </c>
-      <c r="I31">
         <v>0.5</v>
       </c>
-      <c r="J31" t="s">
-        <v>14</v>
+      <c r="I31" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31">
+        <v>80</v>
       </c>
       <c r="K31">
-        <v>80</v>
+        <v>0.4824</v>
       </c>
       <c r="L31">
-        <v>0.4824</v>
-      </c>
-      <c r="M31">
         <v>15.1</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>13063</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D32">
         <v>34.799999999999997</v>
@@ -2285,77 +2188,71 @@
         <v>76.744416200000003</v>
       </c>
       <c r="G32">
-        <v>570.61</v>
+        <v>5.71</v>
       </c>
       <c r="H32">
-        <v>5.71</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="J32">
-        <v>16.420000000000002</v>
+        <v>84.8</v>
       </c>
       <c r="K32">
-        <v>84.8</v>
+        <v>0.41470000000000001</v>
       </c>
       <c r="L32">
-        <v>0.41470000000000001</v>
-      </c>
-      <c r="M32">
         <v>2001.27</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>13065</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D33">
         <v>33.700000000000003</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F33">
         <v>71.640759680000002</v>
       </c>
       <c r="G33">
-        <v>716.79</v>
+        <v>7.17</v>
       </c>
       <c r="H33">
-        <v>7.17</v>
-      </c>
-      <c r="I33">
         <v>0.5</v>
       </c>
-      <c r="J33" t="s">
-        <v>14</v>
+      <c r="I33" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33">
+        <v>69.2</v>
       </c>
       <c r="K33">
-        <v>69.2</v>
+        <v>0.51919999999999999</v>
       </c>
       <c r="L33">
-        <v>0.51919999999999999</v>
-      </c>
-      <c r="M33">
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>13067</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D34">
         <v>26.3</v>
@@ -2367,36 +2264,33 @@
         <v>80.414832799999999</v>
       </c>
       <c r="G34">
-        <v>363.04</v>
+        <v>3.63</v>
       </c>
       <c r="H34">
-        <v>3.63</v>
+        <v>0.5</v>
       </c>
       <c r="I34">
-        <v>0.5</v>
+        <v>9.34</v>
       </c>
       <c r="J34">
-        <v>9.34</v>
+        <v>92.1</v>
       </c>
       <c r="K34">
-        <v>92.1</v>
+        <v>0.4501</v>
       </c>
       <c r="L34">
-        <v>0.4501</v>
-      </c>
-      <c r="M34">
         <v>2210.83</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>13069</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D35">
         <v>35.299999999999997</v>
@@ -2408,36 +2302,33 @@
         <v>74.160570730000003</v>
       </c>
       <c r="G35">
-        <v>609.29999999999995</v>
+        <v>6.09</v>
       </c>
       <c r="H35">
-        <v>6.09</v>
-      </c>
-      <c r="I35">
         <v>0.3</v>
       </c>
-      <c r="J35" t="s">
-        <v>14</v>
+      <c r="I35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35">
+        <v>75.7</v>
       </c>
       <c r="K35">
-        <v>75.7</v>
+        <v>0.4783</v>
       </c>
       <c r="L35">
-        <v>0.4783</v>
-      </c>
-      <c r="M35">
         <v>72.64</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>13071</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D36">
         <v>31.8</v>
@@ -2449,36 +2340,33 @@
         <v>74.371829480000002</v>
       </c>
       <c r="G36">
-        <v>509.79</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H36">
-        <v>5.0999999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="I36">
-        <v>0.5</v>
+        <v>21.93</v>
       </c>
       <c r="J36">
-        <v>21.93</v>
+        <v>74.7</v>
       </c>
       <c r="K36">
-        <v>74.7</v>
+        <v>0.48409999999999997</v>
       </c>
       <c r="L36">
-        <v>0.48409999999999997</v>
-      </c>
-      <c r="M36">
         <v>83.15</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>13073</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D37">
         <v>28.8</v>
@@ -2490,77 +2378,71 @@
         <v>80.336957220000002</v>
       </c>
       <c r="G37">
-        <v>305.05</v>
+        <v>3.05</v>
       </c>
       <c r="H37">
-        <v>3.05</v>
+        <v>0.2</v>
       </c>
       <c r="I37">
-        <v>0.2</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="J37">
-        <v>8.3000000000000007</v>
+        <v>92.7</v>
       </c>
       <c r="K37">
-        <v>92.7</v>
+        <v>0.40039999999999998</v>
       </c>
       <c r="L37">
-        <v>0.40039999999999998</v>
-      </c>
-      <c r="M37">
         <v>519.54</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>13075</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D38">
         <v>30.3</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F38">
         <v>74.938155420000001</v>
       </c>
       <c r="G38">
-        <v>744.04</v>
+        <v>7.44</v>
       </c>
       <c r="H38">
-        <v>7.44</v>
-      </c>
-      <c r="I38">
         <v>0.5</v>
       </c>
-      <c r="J38" t="s">
-        <v>14</v>
+      <c r="I38" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38">
+        <v>79.099999999999994</v>
       </c>
       <c r="K38">
-        <v>79.099999999999994</v>
+        <v>0.46039999999999998</v>
       </c>
       <c r="L38">
-        <v>0.46039999999999998</v>
-      </c>
-      <c r="M38">
         <v>75.2</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>13077</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D39">
         <v>28.5</v>
@@ -2572,77 +2454,71 @@
         <v>78.504036920000004</v>
       </c>
       <c r="G39">
-        <v>425.04</v>
+        <v>4.25</v>
       </c>
       <c r="H39">
-        <v>4.25</v>
+        <v>0.2</v>
       </c>
       <c r="I39">
-        <v>0.2</v>
+        <v>10.1</v>
       </c>
       <c r="J39">
-        <v>10.1</v>
+        <v>89.2</v>
       </c>
       <c r="K39">
-        <v>89.2</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="L39">
-        <v>0.41899999999999998</v>
-      </c>
-      <c r="M39">
         <v>324.89999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>13079</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D40">
         <v>33.6</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F40">
         <v>76.949520509999999</v>
       </c>
       <c r="G40">
-        <v>145.37</v>
+        <v>1.45</v>
       </c>
       <c r="H40">
-        <v>1.45</v>
-      </c>
-      <c r="I40">
         <v>0.2</v>
       </c>
-      <c r="J40" t="s">
-        <v>14</v>
+      <c r="I40" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40">
+        <v>83.1</v>
       </c>
       <c r="K40">
-        <v>83.1</v>
+        <v>0.4662</v>
       </c>
       <c r="L40">
-        <v>0.4662</v>
-      </c>
-      <c r="M40">
         <v>37.93</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>13081</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D41">
         <v>34.700000000000003</v>
@@ -2654,159 +2530,147 @@
         <v>75.217589919999995</v>
       </c>
       <c r="G41">
-        <v>1307.25</v>
+        <v>13.07</v>
       </c>
       <c r="H41">
-        <v>13.07</v>
-      </c>
-      <c r="I41">
         <v>0.7</v>
       </c>
-      <c r="J41" t="s">
-        <v>14</v>
+      <c r="I41" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41">
+        <v>82.8</v>
       </c>
       <c r="K41">
-        <v>82.8</v>
+        <v>0.55449999999999999</v>
       </c>
       <c r="L41">
-        <v>0.55449999999999999</v>
-      </c>
-      <c r="M41">
         <v>83.3</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>13083</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D42">
         <v>34.9</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F42">
         <v>75.761641409999996</v>
       </c>
       <c r="G42">
-        <v>575.6</v>
+        <v>5.76</v>
       </c>
       <c r="H42">
-        <v>5.76</v>
-      </c>
-      <c r="I42">
         <v>0.2</v>
       </c>
-      <c r="J42" t="s">
-        <v>14</v>
+      <c r="I42" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42">
+        <v>80.7</v>
       </c>
       <c r="K42">
-        <v>80.7</v>
+        <v>0.44369999999999998</v>
       </c>
       <c r="L42">
-        <v>0.44369999999999998</v>
-      </c>
-      <c r="M42">
         <v>93.1</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>13085</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D43">
         <v>28.4</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F43">
         <v>76.883992059999997</v>
       </c>
       <c r="G43">
-        <v>407.52</v>
+        <v>4.08</v>
       </c>
       <c r="H43">
-        <v>4.08</v>
-      </c>
-      <c r="I43">
         <v>0.2</v>
       </c>
-      <c r="J43" t="s">
-        <v>14</v>
+      <c r="I43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43">
+        <v>87.2</v>
       </c>
       <c r="K43">
-        <v>87.2</v>
+        <v>0.43380000000000002</v>
       </c>
       <c r="L43">
-        <v>0.43380000000000002</v>
-      </c>
-      <c r="M43">
         <v>116.38</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>13087</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D44">
         <v>28.2</v>
       </c>
       <c r="E44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F44">
         <v>73.982647209999996</v>
       </c>
       <c r="G44">
-        <v>979.49</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="H44">
-        <v>9.7899999999999991</v>
+        <v>0.6</v>
       </c>
       <c r="I44">
-        <v>0.6</v>
+        <v>41.66</v>
       </c>
       <c r="J44">
-        <v>41.66</v>
+        <v>82.5</v>
       </c>
       <c r="K44">
-        <v>82.5</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="L44">
-        <v>0.47899999999999998</v>
-      </c>
-      <c r="M44">
         <v>44.68</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>13089</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D45">
         <v>25.6</v>
@@ -2818,118 +2682,109 @@
         <v>80.028290420000005</v>
       </c>
       <c r="G45">
-        <v>441.77</v>
+        <v>4.42</v>
       </c>
       <c r="H45">
-        <v>4.42</v>
+        <v>1.4</v>
       </c>
       <c r="I45">
-        <v>1.4</v>
+        <v>10.93</v>
       </c>
       <c r="J45">
-        <v>10.93</v>
+        <v>89.3</v>
       </c>
       <c r="K45">
-        <v>89.3</v>
+        <v>0.4894</v>
       </c>
       <c r="L45">
-        <v>0.4894</v>
-      </c>
-      <c r="M45">
         <v>2798.79</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>13091</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D46">
         <v>30.5</v>
       </c>
       <c r="E46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F46">
         <v>74.255118999999993</v>
       </c>
       <c r="G46">
-        <v>775.96</v>
+        <v>7.76</v>
       </c>
       <c r="H46">
-        <v>7.76</v>
+        <v>0.5</v>
       </c>
       <c r="I46">
-        <v>0.5</v>
+        <v>48.53</v>
       </c>
       <c r="J46">
-        <v>48.53</v>
+        <v>85.6</v>
       </c>
       <c r="K46">
-        <v>85.6</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="L46">
-        <v>0.46899999999999997</v>
-      </c>
-      <c r="M46">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>13093</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D47">
         <v>33.700000000000003</v>
       </c>
       <c r="E47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F47">
         <v>78.080993890000002</v>
       </c>
       <c r="G47">
-        <v>691.18</v>
+        <v>6.91</v>
       </c>
       <c r="H47">
-        <v>6.91</v>
-      </c>
-      <c r="I47">
         <v>0.5</v>
       </c>
-      <c r="J47" t="s">
-        <v>14</v>
+      <c r="I47" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47">
+        <v>77.7</v>
       </c>
       <c r="K47">
-        <v>77.7</v>
+        <v>0.48149999999999998</v>
       </c>
       <c r="L47">
-        <v>0.48149999999999998</v>
-      </c>
-      <c r="M47">
         <v>34.979999999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>13095</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D48">
         <v>33.4</v>
@@ -2941,36 +2796,33 @@
         <v>74.24330569</v>
       </c>
       <c r="G48">
-        <v>1104.98</v>
+        <v>11.05</v>
       </c>
       <c r="H48">
-        <v>11.05</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I48">
-        <v>1.1000000000000001</v>
+        <v>14.78</v>
       </c>
       <c r="J48">
-        <v>14.78</v>
+        <v>83.4</v>
       </c>
       <c r="K48">
-        <v>83.4</v>
+        <v>0.49330000000000002</v>
       </c>
       <c r="L48">
-        <v>0.49330000000000002</v>
-      </c>
-      <c r="M48">
         <v>272.95</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>13097</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D49">
         <v>30.2</v>
@@ -2982,118 +2834,109 @@
         <v>77.394548259999993</v>
       </c>
       <c r="G49">
-        <v>856.22</v>
+        <v>8.56</v>
       </c>
       <c r="H49">
-        <v>8.56</v>
+        <v>0.5</v>
       </c>
       <c r="I49">
-        <v>0.5</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="J49">
-        <v>17.079999999999998</v>
+        <v>87.8</v>
       </c>
       <c r="K49">
-        <v>87.8</v>
+        <v>0.41</v>
       </c>
       <c r="L49">
-        <v>0.41</v>
-      </c>
-      <c r="M49">
         <v>716.09</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>13099</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D50">
         <v>34.6</v>
       </c>
       <c r="E50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F50">
         <v>74.491217520000006</v>
       </c>
       <c r="G50">
-        <v>985.46</v>
+        <v>9.85</v>
       </c>
       <c r="H50">
-        <v>9.85</v>
-      </c>
-      <c r="I50">
         <v>0.3</v>
       </c>
-      <c r="J50" t="s">
-        <v>14</v>
+      <c r="I50" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50">
+        <v>80.400000000000006</v>
       </c>
       <c r="K50">
-        <v>80.400000000000006</v>
+        <v>0.49959999999999999</v>
       </c>
       <c r="L50">
-        <v>0.49959999999999999</v>
-      </c>
-      <c r="M50">
         <v>20.12</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>13101</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D51">
         <v>27.7</v>
       </c>
       <c r="E51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F51">
         <v>79.573171369999997</v>
       </c>
       <c r="G51">
-        <v>247.71</v>
-      </c>
-      <c r="H51">
         <v>2.48</v>
       </c>
+      <c r="H51" t="s">
+        <v>13</v>
+      </c>
       <c r="I51" t="s">
-        <v>14</v>
-      </c>
-      <c r="J51" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="J51">
+        <v>74.2</v>
       </c>
       <c r="K51">
-        <v>74.2</v>
+        <v>0.50019999999999998</v>
       </c>
       <c r="L51">
-        <v>0.50019999999999998</v>
-      </c>
-      <c r="M51">
         <v>9.4700000000000006</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>13103</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D52">
         <v>36</v>
@@ -3105,77 +2948,71 @@
         <v>76.097469689999997</v>
       </c>
       <c r="G52">
-        <v>357.36</v>
+        <v>3.57</v>
       </c>
       <c r="H52">
-        <v>3.57</v>
+        <v>0.1</v>
       </c>
       <c r="I52">
-        <v>0.1</v>
+        <v>17.11</v>
       </c>
       <c r="J52">
-        <v>17.11</v>
+        <v>88.3</v>
       </c>
       <c r="K52">
-        <v>88.3</v>
+        <v>0.44090000000000001</v>
       </c>
       <c r="L52">
-        <v>0.44090000000000001</v>
-      </c>
-      <c r="M52">
         <v>126.3</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>13105</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D53">
         <v>31.8</v>
       </c>
       <c r="E53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F53">
         <v>74.524143210000005</v>
       </c>
       <c r="G53">
-        <v>720.24</v>
+        <v>7.2</v>
       </c>
       <c r="H53">
-        <v>7.2</v>
-      </c>
-      <c r="I53">
         <v>0.2</v>
       </c>
-      <c r="J53" t="s">
-        <v>14</v>
+      <c r="I53" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53">
+        <v>78.400000000000006</v>
       </c>
       <c r="K53">
-        <v>78.400000000000006</v>
+        <v>0.47020000000000001</v>
       </c>
       <c r="L53">
-        <v>0.47020000000000001</v>
-      </c>
-      <c r="M53">
         <v>54.59</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>13107</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D54">
         <v>33.5</v>
@@ -3187,118 +3024,109 @@
         <v>72.595447100000001</v>
       </c>
       <c r="G54">
-        <v>823.06</v>
+        <v>8.23</v>
       </c>
       <c r="H54">
-        <v>8.23</v>
-      </c>
-      <c r="I54">
         <v>0.4</v>
       </c>
-      <c r="J54" t="s">
-        <v>14</v>
+      <c r="I54" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54">
+        <v>78.599999999999994</v>
       </c>
       <c r="K54">
-        <v>78.599999999999994</v>
+        <v>0.46100000000000002</v>
       </c>
       <c r="L54">
-        <v>0.46100000000000002</v>
-      </c>
-      <c r="M54">
         <v>33.11</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>13109</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D55">
         <v>32.799999999999997</v>
       </c>
       <c r="E55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F55">
         <v>74.578216409999996</v>
       </c>
       <c r="G55">
-        <v>906.97</v>
+        <v>9.07</v>
       </c>
       <c r="H55">
-        <v>9.07</v>
-      </c>
-      <c r="I55">
         <v>0.5</v>
       </c>
-      <c r="J55" t="s">
-        <v>14</v>
+      <c r="I55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55">
+        <v>76.2</v>
       </c>
       <c r="K55">
-        <v>76.2</v>
+        <v>0.45739999999999997</v>
       </c>
       <c r="L55">
-        <v>0.45739999999999997</v>
-      </c>
-      <c r="M55">
         <v>58.43</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>13111</v>
       </c>
       <c r="B56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D56">
         <v>27.7</v>
       </c>
       <c r="E56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F56">
         <v>76.581104740000001</v>
       </c>
       <c r="G56">
-        <v>417.37</v>
+        <v>4.17</v>
       </c>
       <c r="H56">
-        <v>4.17</v>
-      </c>
-      <c r="I56">
         <v>0.1</v>
       </c>
-      <c r="J56" t="s">
-        <v>14</v>
+      <c r="I56" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56">
+        <v>86.6</v>
       </c>
       <c r="K56">
-        <v>86.6</v>
+        <v>0.45390000000000003</v>
       </c>
       <c r="L56">
-        <v>0.45390000000000003</v>
-      </c>
-      <c r="M56">
         <v>65.599999999999994</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>13113</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D57">
         <v>33.299999999999997</v>
@@ -3310,36 +3138,33 @@
         <v>80.869552569999996</v>
       </c>
       <c r="G57">
-        <v>342.1</v>
+        <v>3.42</v>
       </c>
       <c r="H57">
-        <v>3.42</v>
-      </c>
-      <c r="I57">
         <v>0.2</v>
       </c>
-      <c r="J57" t="s">
-        <v>14</v>
+      <c r="I57" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57">
+        <v>95.3</v>
       </c>
       <c r="K57">
-        <v>95.3</v>
+        <v>0.43690000000000001</v>
       </c>
       <c r="L57">
-        <v>0.43690000000000001</v>
-      </c>
-      <c r="M57">
         <v>577.76</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>13115</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D58">
         <v>34.5</v>
@@ -3351,36 +3176,33 @@
         <v>75.764549450000004</v>
       </c>
       <c r="G58">
-        <v>1024.95</v>
+        <v>10.25</v>
       </c>
       <c r="H58">
-        <v>10.25</v>
+        <v>0.3</v>
       </c>
       <c r="I58">
-        <v>0.3</v>
+        <v>22.34</v>
       </c>
       <c r="J58">
-        <v>22.34</v>
+        <v>82.4</v>
       </c>
       <c r="K58">
-        <v>82.4</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="L58">
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="M58">
         <v>190.99</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>13117</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D59">
         <v>30</v>
@@ -3392,77 +3214,71 @@
         <v>81.511521720000005</v>
       </c>
       <c r="G59">
-        <v>193.63</v>
+        <v>1.94</v>
       </c>
       <c r="H59">
-        <v>1.94</v>
+        <v>0.1</v>
       </c>
       <c r="I59">
-        <v>0.1</v>
+        <v>6.14</v>
       </c>
       <c r="J59">
-        <v>6.14</v>
+        <v>93</v>
       </c>
       <c r="K59">
-        <v>93</v>
+        <v>0.4017</v>
       </c>
       <c r="L59">
-        <v>0.4017</v>
-      </c>
-      <c r="M59">
         <v>1017.06</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>13119</v>
       </c>
       <c r="B60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D60">
         <v>30.7</v>
       </c>
       <c r="E60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F60">
         <v>74.418458990000005</v>
       </c>
       <c r="G60">
-        <v>687.27</v>
+        <v>6.87</v>
       </c>
       <c r="H60">
-        <v>6.87</v>
-      </c>
-      <c r="I60">
         <v>0.2</v>
       </c>
-      <c r="J60" t="s">
-        <v>14</v>
+      <c r="I60" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60">
+        <v>82.3</v>
       </c>
       <c r="K60">
-        <v>82.3</v>
+        <v>0.49109999999999998</v>
       </c>
       <c r="L60">
-        <v>0.49109999999999998</v>
-      </c>
-      <c r="M60">
         <v>87.04</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>13121</v>
       </c>
       <c r="B61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D61">
         <v>25.1</v>
@@ -3474,118 +3290,109 @@
         <v>79.325199209999994</v>
       </c>
       <c r="G61">
-        <v>504.59</v>
+        <v>5.05</v>
       </c>
       <c r="H61">
-        <v>5.05</v>
+        <v>1.7</v>
       </c>
       <c r="I61">
-        <v>1.7</v>
+        <v>11.94</v>
       </c>
       <c r="J61">
-        <v>11.94</v>
+        <v>92.6</v>
       </c>
       <c r="K61">
-        <v>92.6</v>
+        <v>0.54139999999999999</v>
       </c>
       <c r="L61">
-        <v>0.54139999999999999</v>
-      </c>
-      <c r="M61">
         <v>1967.26</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>13123</v>
       </c>
       <c r="B62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D62">
         <v>28.6</v>
       </c>
       <c r="E62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F62">
         <v>76.933715289999995</v>
       </c>
       <c r="G62">
-        <v>335.63</v>
+        <v>3.36</v>
       </c>
       <c r="H62">
-        <v>3.36</v>
-      </c>
-      <c r="I62">
         <v>0.2</v>
       </c>
-      <c r="J62" t="s">
-        <v>14</v>
+      <c r="I62" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62">
+        <v>81.7</v>
       </c>
       <c r="K62">
-        <v>81.7</v>
+        <v>0.45610000000000001</v>
       </c>
       <c r="L62">
-        <v>0.45610000000000001</v>
-      </c>
-      <c r="M62">
         <v>71.36</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>13125</v>
       </c>
       <c r="B63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D63">
         <v>29.5</v>
       </c>
       <c r="E63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F63">
         <v>75.919968659999995</v>
       </c>
       <c r="G63">
-        <v>198.81</v>
+        <v>1.99</v>
       </c>
       <c r="H63">
-        <v>1.99</v>
-      </c>
-      <c r="I63">
         <v>0.3</v>
       </c>
-      <c r="J63" t="s">
-        <v>14</v>
+      <c r="I63" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63">
+        <v>78.2</v>
       </c>
       <c r="K63">
-        <v>78.2</v>
+        <v>0.45379999999999998</v>
       </c>
       <c r="L63">
-        <v>0.45379999999999998</v>
-      </c>
-      <c r="M63">
         <v>20.84</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>13127</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D64">
         <v>28.7</v>
@@ -3597,36 +3404,33 @@
         <v>77.299829110000005</v>
       </c>
       <c r="G64">
-        <v>654.89</v>
+        <v>6.55</v>
       </c>
       <c r="H64">
-        <v>6.55</v>
+        <v>0.5</v>
       </c>
       <c r="I64">
-        <v>0.5</v>
+        <v>24.62</v>
       </c>
       <c r="J64">
-        <v>24.62</v>
+        <v>88.1</v>
       </c>
       <c r="K64">
-        <v>88.1</v>
+        <v>0.51229999999999998</v>
       </c>
       <c r="L64">
-        <v>0.51229999999999998</v>
-      </c>
-      <c r="M64">
         <v>201.33</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>13129</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D65">
         <v>26.8</v>
@@ -3638,36 +3442,33 @@
         <v>75.868841750000001</v>
       </c>
       <c r="G65">
-        <v>749.17</v>
+        <v>7.49</v>
       </c>
       <c r="H65">
-        <v>7.49</v>
-      </c>
-      <c r="I65">
         <v>0.1</v>
       </c>
-      <c r="J65" t="s">
-        <v>14</v>
+      <c r="I65" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65">
+        <v>77.900000000000006</v>
       </c>
       <c r="K65">
-        <v>77.900000000000006</v>
+        <v>0.46460000000000001</v>
       </c>
       <c r="L65">
-        <v>0.46460000000000001</v>
-      </c>
-      <c r="M65">
         <v>160.47999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>13131</v>
       </c>
       <c r="B66" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D66">
         <v>34.6</v>
@@ -3679,77 +3480,71 @@
         <v>76.272210220000005</v>
       </c>
       <c r="G66">
-        <v>681.93</v>
+        <v>6.82</v>
       </c>
       <c r="H66">
-        <v>6.82</v>
-      </c>
-      <c r="I66">
         <v>0.3</v>
       </c>
-      <c r="J66" t="s">
-        <v>14</v>
+      <c r="I66" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66">
+        <v>80.099999999999994</v>
       </c>
       <c r="K66">
-        <v>80.099999999999994</v>
+        <v>0.45989999999999998</v>
       </c>
       <c r="L66">
-        <v>0.45989999999999998</v>
-      </c>
-      <c r="M66">
         <v>54.63</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>13133</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D67">
         <v>31.3</v>
       </c>
       <c r="E67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F67">
         <v>77.594119750000004</v>
       </c>
       <c r="G67">
-        <v>702.96</v>
+        <v>7.03</v>
       </c>
       <c r="H67">
-        <v>7.03</v>
-      </c>
-      <c r="I67">
         <v>0.2</v>
       </c>
-      <c r="J67" t="s">
-        <v>14</v>
+      <c r="I67" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67">
+        <v>85.3</v>
       </c>
       <c r="K67">
-        <v>85.3</v>
+        <v>0.56040000000000001</v>
       </c>
       <c r="L67">
-        <v>0.56040000000000001</v>
-      </c>
-      <c r="M67">
         <v>44.75</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>13135</v>
       </c>
       <c r="B68" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D68">
         <v>30.1</v>
@@ -3761,77 +3556,71 @@
         <v>80.83189892</v>
       </c>
       <c r="G68">
-        <v>280.13</v>
+        <v>2.8</v>
       </c>
       <c r="H68">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="I68">
-        <v>0.4</v>
+        <v>8.01</v>
       </c>
       <c r="J68">
-        <v>8.01</v>
+        <v>87.7</v>
       </c>
       <c r="K68">
-        <v>87.7</v>
+        <v>0.42670000000000002</v>
       </c>
       <c r="L68">
-        <v>0.42670000000000002</v>
-      </c>
-      <c r="M68">
         <v>2124.94</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>13137</v>
       </c>
       <c r="B69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D69">
         <v>29.6</v>
       </c>
       <c r="E69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F69">
         <v>76.91687383</v>
       </c>
       <c r="G69">
-        <v>253.4</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H69">
-        <v>2.5299999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="I69">
-        <v>0.2</v>
+        <v>30.89</v>
       </c>
       <c r="J69">
-        <v>30.89</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="K69">
-        <v>79.599999999999994</v>
+        <v>0.43480000000000002</v>
       </c>
       <c r="L69">
-        <v>0.43480000000000002</v>
-      </c>
-      <c r="M69">
         <v>161.21</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>13139</v>
       </c>
       <c r="B70" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D70">
         <v>31.9</v>
@@ -3843,241 +3632,223 @@
         <v>79.259533959999999</v>
       </c>
       <c r="G70">
-        <v>394.37</v>
+        <v>3.94</v>
       </c>
       <c r="H70">
-        <v>3.94</v>
+        <v>0.2</v>
       </c>
       <c r="I70">
-        <v>0.2</v>
+        <v>12.72</v>
       </c>
       <c r="J70">
-        <v>12.72</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="K70">
-        <v>79.099999999999994</v>
+        <v>0.45960000000000001</v>
       </c>
       <c r="L70">
-        <v>0.45960000000000001</v>
-      </c>
-      <c r="M70">
         <v>505.52</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>13141</v>
       </c>
       <c r="B71" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C71" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D71">
         <v>31.1</v>
       </c>
       <c r="E71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F71">
         <v>75.406949830000002</v>
       </c>
       <c r="G71">
-        <v>442.94</v>
+        <v>4.43</v>
       </c>
       <c r="H71">
-        <v>4.43</v>
-      </c>
-      <c r="I71">
         <v>0.5</v>
       </c>
-      <c r="J71" t="s">
-        <v>14</v>
+      <c r="I71" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71">
+        <v>74.2</v>
       </c>
       <c r="K71">
-        <v>74.2</v>
+        <v>0.46970000000000001</v>
       </c>
       <c r="L71">
-        <v>0.46970000000000001</v>
-      </c>
-      <c r="M71">
         <v>18.079999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>13143</v>
       </c>
       <c r="B72" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D72">
         <v>27.7</v>
       </c>
       <c r="E72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F72">
         <v>72.818206009999997</v>
       </c>
       <c r="G72">
-        <v>546.96</v>
+        <v>5.47</v>
       </c>
       <c r="H72">
-        <v>5.47</v>
+        <v>0.1</v>
       </c>
       <c r="I72">
-        <v>0.1</v>
+        <v>36.92</v>
       </c>
       <c r="J72">
-        <v>36.92</v>
+        <v>81.2</v>
       </c>
       <c r="K72">
-        <v>81.2</v>
+        <v>0.43940000000000001</v>
       </c>
       <c r="L72">
-        <v>0.43940000000000001</v>
-      </c>
-      <c r="M72">
         <v>103.58</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>13145</v>
       </c>
       <c r="B73" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D73">
         <v>32.200000000000003</v>
       </c>
       <c r="E73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F73">
         <v>80.063933700000007</v>
       </c>
       <c r="G73">
-        <v>313.64</v>
+        <v>3.14</v>
       </c>
       <c r="H73">
-        <v>3.14</v>
-      </c>
-      <c r="I73">
         <v>0.1</v>
       </c>
-      <c r="J73" t="s">
-        <v>14</v>
+      <c r="I73" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73">
+        <v>92.2</v>
       </c>
       <c r="K73">
-        <v>92.2</v>
+        <v>0.44359999999999999</v>
       </c>
       <c r="L73">
-        <v>0.44359999999999999</v>
-      </c>
-      <c r="M73">
         <v>73.53</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>13147</v>
       </c>
       <c r="B74" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D74">
         <v>31.7</v>
       </c>
       <c r="E74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F74">
         <v>77.180740970000002</v>
       </c>
       <c r="G74">
-        <v>637.02</v>
+        <v>6.37</v>
       </c>
       <c r="H74">
-        <v>6.37</v>
-      </c>
-      <c r="I74">
         <v>0.2</v>
       </c>
-      <c r="J74" t="s">
-        <v>14</v>
+      <c r="I74" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74">
+        <v>81.5</v>
       </c>
       <c r="K74">
-        <v>81.5</v>
+        <v>0.44979999999999998</v>
       </c>
       <c r="L74">
-        <v>0.44979999999999998</v>
-      </c>
-      <c r="M74">
         <v>110.89</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>13149</v>
       </c>
       <c r="B75" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C75" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D75">
         <v>31.4</v>
       </c>
       <c r="E75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F75">
         <v>74.566920210000006</v>
       </c>
       <c r="G75">
-        <v>476.11</v>
+        <v>4.76</v>
       </c>
       <c r="H75">
-        <v>4.76</v>
-      </c>
-      <c r="I75">
         <v>0.1</v>
       </c>
-      <c r="J75" t="s">
-        <v>14</v>
+      <c r="I75" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75">
+        <v>79.7</v>
       </c>
       <c r="K75">
-        <v>79.7</v>
+        <v>0.40379999999999999</v>
       </c>
       <c r="L75">
-        <v>0.40379999999999999</v>
-      </c>
-      <c r="M75">
         <v>39.65</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>13151</v>
       </c>
       <c r="B76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D76">
         <v>34.299999999999997</v>
@@ -4089,36 +3860,33 @@
         <v>77.480606359999996</v>
       </c>
       <c r="G76">
-        <v>259.5</v>
+        <v>2.6</v>
       </c>
       <c r="H76">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="I76">
-        <v>0.5</v>
+        <v>7.25</v>
       </c>
       <c r="J76">
-        <v>7.25</v>
+        <v>91.2</v>
       </c>
       <c r="K76">
-        <v>91.2</v>
+        <v>0.39190000000000003</v>
       </c>
       <c r="L76">
-        <v>0.39190000000000003</v>
-      </c>
-      <c r="M76">
         <v>707.22</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>13153</v>
       </c>
       <c r="B77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D77">
         <v>32.200000000000003</v>
@@ -4130,77 +3898,71 @@
         <v>77.672782470000001</v>
       </c>
       <c r="G77">
-        <v>498.62</v>
+        <v>4.99</v>
       </c>
       <c r="H77">
-        <v>4.99</v>
+        <v>0.3</v>
       </c>
       <c r="I77">
-        <v>0.3</v>
+        <v>12.67</v>
       </c>
       <c r="J77">
-        <v>12.67</v>
+        <v>91.6</v>
       </c>
       <c r="K77">
-        <v>91.6</v>
+        <v>0.43269999999999997</v>
       </c>
       <c r="L77">
-        <v>0.43269999999999997</v>
-      </c>
-      <c r="M77">
         <v>408.22</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>13155</v>
       </c>
       <c r="B78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C78" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D78">
         <v>31.5</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F78">
         <v>74.722082520000001</v>
       </c>
       <c r="G78">
-        <v>764.94</v>
+        <v>7.65</v>
       </c>
       <c r="H78">
-        <v>7.65</v>
-      </c>
-      <c r="I78">
         <v>0.9</v>
       </c>
-      <c r="J78" t="s">
-        <v>14</v>
+      <c r="I78" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78">
+        <v>81.5</v>
       </c>
       <c r="K78">
-        <v>81.5</v>
+        <v>0.48139999999999999</v>
       </c>
       <c r="L78">
-        <v>0.48139999999999999</v>
-      </c>
-      <c r="M78">
         <v>26.3</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>13157</v>
       </c>
       <c r="B79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D79">
         <v>26.7</v>
@@ -4212,364 +3974,337 @@
         <v>76.323730459999993</v>
       </c>
       <c r="G79">
-        <v>419.32</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="H79">
-        <v>4.1900000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="I79">
-        <v>0.2</v>
+        <v>13.7</v>
       </c>
       <c r="J79">
-        <v>13.7</v>
+        <v>84.1</v>
       </c>
       <c r="K79">
-        <v>84.1</v>
+        <v>0.42909999999999998</v>
       </c>
       <c r="L79">
-        <v>0.42909999999999998</v>
-      </c>
-      <c r="M79">
         <v>199.86</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>13159</v>
       </c>
       <c r="B80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D80">
         <v>32.5</v>
       </c>
       <c r="E80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F80">
         <v>76.597456570000006</v>
       </c>
       <c r="G80">
-        <v>452.98</v>
+        <v>4.53</v>
       </c>
       <c r="H80">
-        <v>4.53</v>
-      </c>
-      <c r="I80">
         <v>0.2</v>
       </c>
-      <c r="J80" t="s">
-        <v>14</v>
+      <c r="I80" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80">
+        <v>82.8</v>
       </c>
       <c r="K80">
-        <v>82.8</v>
+        <v>0.41589999999999999</v>
       </c>
       <c r="L80">
-        <v>0.41589999999999999</v>
-      </c>
-      <c r="M80">
         <v>37.770000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>13161</v>
       </c>
       <c r="B81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D81">
         <v>30.2</v>
       </c>
       <c r="E81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F81">
         <v>72.042330750000005</v>
       </c>
       <c r="G81">
-        <v>632.53</v>
+        <v>6.33</v>
       </c>
       <c r="H81">
-        <v>6.33</v>
-      </c>
-      <c r="I81">
         <v>0.1</v>
       </c>
-      <c r="J81" t="s">
-        <v>14</v>
+      <c r="I81" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81">
+        <v>79.3</v>
       </c>
       <c r="K81">
-        <v>79.3</v>
+        <v>0.43569999999999998</v>
       </c>
       <c r="L81">
-        <v>0.43569999999999998</v>
-      </c>
-      <c r="M81">
         <v>45.44</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>13163</v>
       </c>
       <c r="B82" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C82" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D82">
         <v>32.9</v>
       </c>
       <c r="E82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F82">
         <v>73.291653429999997</v>
       </c>
       <c r="G82">
-        <v>1029.7</v>
+        <v>10.3</v>
       </c>
       <c r="H82">
-        <v>10.3</v>
-      </c>
-      <c r="I82">
         <v>0.4</v>
       </c>
-      <c r="J82" t="s">
-        <v>14</v>
+      <c r="I82" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82">
+        <v>76.400000000000006</v>
       </c>
       <c r="K82">
-        <v>76.400000000000006</v>
+        <v>0.47299999999999998</v>
       </c>
       <c r="L82">
-        <v>0.47299999999999998</v>
-      </c>
-      <c r="M82">
         <v>29.66</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>13165</v>
       </c>
       <c r="B83" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D83">
         <v>30.7</v>
       </c>
       <c r="E83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F83">
         <v>74.562324610000005</v>
       </c>
       <c r="G83">
-        <v>1002.82</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="H83">
-        <v>10.029999999999999</v>
-      </c>
-      <c r="I83">
         <v>0.4</v>
       </c>
-      <c r="J83" t="s">
-        <v>14</v>
+      <c r="I83" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83">
+        <v>79.3</v>
       </c>
       <c r="K83">
-        <v>79.3</v>
+        <v>0.44169999999999998</v>
       </c>
       <c r="L83">
-        <v>0.44169999999999998</v>
-      </c>
-      <c r="M83">
         <v>25.32</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>13167</v>
       </c>
       <c r="B84" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C84" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D84">
         <v>33.799999999999997</v>
       </c>
       <c r="E84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F84">
         <v>76.145951460000006</v>
       </c>
       <c r="G84">
-        <v>453.19</v>
+        <v>4.53</v>
       </c>
       <c r="H84">
-        <v>4.53</v>
-      </c>
-      <c r="I84">
         <v>0.2</v>
       </c>
-      <c r="J84" t="s">
-        <v>14</v>
+      <c r="I84" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84">
+        <v>75.099999999999994</v>
       </c>
       <c r="K84">
-        <v>75.099999999999994</v>
+        <v>0.42080000000000001</v>
       </c>
       <c r="L84">
-        <v>0.42080000000000001</v>
-      </c>
-      <c r="M84">
         <v>31.98</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>13169</v>
       </c>
       <c r="B85" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C85" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D85">
         <v>31</v>
       </c>
       <c r="E85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F85">
         <v>78.852138299999993</v>
       </c>
       <c r="G85">
-        <v>734.73</v>
+        <v>7.35</v>
       </c>
       <c r="H85">
-        <v>7.35</v>
-      </c>
-      <c r="I85">
         <v>0.1</v>
       </c>
-      <c r="J85" t="s">
-        <v>14</v>
+      <c r="I85" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85">
+        <v>89.1</v>
       </c>
       <c r="K85">
-        <v>89.1</v>
+        <v>0.42709999999999998</v>
       </c>
       <c r="L85">
-        <v>0.42709999999999998</v>
-      </c>
-      <c r="M85">
         <v>72.55</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>13171</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C86" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D86">
         <v>33.200000000000003</v>
       </c>
       <c r="E86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F86">
         <v>74.791309369999993</v>
       </c>
       <c r="G86">
-        <v>433.11</v>
+        <v>4.33</v>
       </c>
       <c r="H86">
-        <v>4.33</v>
-      </c>
-      <c r="I86">
         <v>0.3</v>
       </c>
-      <c r="J86" t="s">
-        <v>14</v>
+      <c r="I86" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86">
+        <v>87</v>
       </c>
       <c r="K86">
-        <v>87</v>
+        <v>0.4783</v>
       </c>
       <c r="L86">
-        <v>0.4783</v>
-      </c>
-      <c r="M86">
         <v>101.75</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>13173</v>
       </c>
       <c r="B87" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C87" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D87">
         <v>31.9</v>
       </c>
       <c r="E87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F87">
         <v>76.562311789999995</v>
       </c>
       <c r="G87">
-        <v>457.82</v>
+        <v>4.58</v>
       </c>
       <c r="H87">
-        <v>4.58</v>
-      </c>
-      <c r="I87">
         <v>0.2</v>
       </c>
-      <c r="J87" t="s">
-        <v>14</v>
+      <c r="I87" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87">
+        <v>80</v>
       </c>
       <c r="K87">
-        <v>80</v>
+        <v>0.46870000000000001</v>
       </c>
       <c r="L87">
-        <v>0.46870000000000001</v>
-      </c>
-      <c r="M87">
         <v>52.81</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>13175</v>
       </c>
       <c r="B88" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C88" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D88">
         <v>37.1</v>
@@ -4581,36 +4316,33 @@
         <v>74.859368930000002</v>
       </c>
       <c r="G88">
-        <v>595.63</v>
+        <v>5.96</v>
       </c>
       <c r="H88">
-        <v>5.96</v>
+        <v>0.5</v>
       </c>
       <c r="I88">
-        <v>0.5</v>
+        <v>27.34</v>
       </c>
       <c r="J88">
-        <v>27.34</v>
+        <v>85.9</v>
       </c>
       <c r="K88">
-        <v>85.9</v>
+        <v>0.49969999999999998</v>
       </c>
       <c r="L88">
-        <v>0.49969999999999998</v>
-      </c>
-      <c r="M88">
         <v>58.72</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>13177</v>
       </c>
       <c r="B89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C89" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D89">
         <v>33.1</v>
@@ -4622,36 +4354,33 @@
         <v>76.71738062</v>
       </c>
       <c r="G89">
-        <v>215.82</v>
+        <v>2.16</v>
       </c>
       <c r="H89">
-        <v>2.16</v>
-      </c>
-      <c r="I89">
         <v>0.2</v>
       </c>
-      <c r="J89" t="s">
-        <v>14</v>
+      <c r="I89" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89">
+        <v>90.9</v>
       </c>
       <c r="K89">
-        <v>90.9</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="L89">
-        <v>0.39700000000000002</v>
-      </c>
-      <c r="M89">
         <v>82.9</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>13179</v>
       </c>
       <c r="B90" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C90" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D90">
         <v>36</v>
@@ -4663,118 +4392,109 @@
         <v>76.340470240000002</v>
       </c>
       <c r="G90">
-        <v>425.05</v>
+        <v>4.25</v>
       </c>
       <c r="H90">
-        <v>4.25</v>
+        <v>0.5</v>
       </c>
       <c r="I90">
-        <v>0.5</v>
+        <v>16.28</v>
       </c>
       <c r="J90">
-        <v>16.28</v>
+        <v>90.7</v>
       </c>
       <c r="K90">
-        <v>90.7</v>
+        <v>0.39710000000000001</v>
       </c>
       <c r="L90">
-        <v>0.39710000000000001</v>
-      </c>
-      <c r="M90">
         <v>118.79</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>13181</v>
       </c>
       <c r="B91" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C91" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D91">
         <v>28.4</v>
       </c>
       <c r="E91" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F91">
         <v>76.542718930000007</v>
       </c>
       <c r="G91">
-        <v>375.7</v>
+        <v>3.76</v>
       </c>
       <c r="H91">
-        <v>3.76</v>
-      </c>
-      <c r="I91">
         <v>0.2</v>
       </c>
-      <c r="J91" t="s">
-        <v>14</v>
+      <c r="I91" t="s">
+        <v>13</v>
+      </c>
+      <c r="J91">
+        <v>82.1</v>
       </c>
       <c r="K91">
-        <v>82.1</v>
+        <v>0.4995</v>
       </c>
       <c r="L91">
-        <v>0.4995</v>
-      </c>
-      <c r="M91">
         <v>37.340000000000003</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>13183</v>
       </c>
       <c r="B92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C92" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D92">
         <v>34.9</v>
       </c>
       <c r="E92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F92">
         <v>80.205580330000004</v>
       </c>
       <c r="G92">
-        <v>476.03</v>
+        <v>4.76</v>
       </c>
       <c r="H92">
-        <v>4.76</v>
-      </c>
-      <c r="I92">
         <v>0.1</v>
       </c>
-      <c r="J92" t="s">
-        <v>14</v>
+      <c r="I92" t="s">
+        <v>13</v>
+      </c>
+      <c r="J92">
+        <v>87.7</v>
       </c>
       <c r="K92">
-        <v>87.7</v>
+        <v>0.37869999999999998</v>
       </c>
       <c r="L92">
-        <v>0.37869999999999998</v>
-      </c>
-      <c r="M92">
         <v>46.68</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>13185</v>
       </c>
       <c r="B93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C93" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D93">
         <v>36.299999999999997</v>
@@ -4786,569 +4506,527 @@
         <v>76.464283320000007</v>
       </c>
       <c r="G93">
-        <v>461.42</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="H93">
-        <v>4.6100000000000003</v>
-      </c>
-      <c r="I93">
         <v>0.6</v>
       </c>
-      <c r="J93" t="s">
-        <v>14</v>
+      <c r="I93" t="s">
+        <v>13</v>
+      </c>
+      <c r="J93">
+        <v>86.6</v>
       </c>
       <c r="K93">
-        <v>86.6</v>
+        <v>0.51790000000000003</v>
       </c>
       <c r="L93">
-        <v>0.51790000000000003</v>
-      </c>
-      <c r="M93">
         <v>232.05</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>13187</v>
       </c>
       <c r="B94" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C94" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D94">
         <v>32</v>
       </c>
       <c r="E94" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F94">
         <v>77.293350040000007</v>
       </c>
       <c r="G94">
-        <v>271.36</v>
+        <v>2.71</v>
       </c>
       <c r="H94">
-        <v>2.71</v>
-      </c>
-      <c r="I94">
         <v>0.1</v>
       </c>
-      <c r="J94" t="s">
-        <v>14</v>
+      <c r="I94" t="s">
+        <v>13</v>
+      </c>
+      <c r="J94">
+        <v>84.8</v>
       </c>
       <c r="K94">
-        <v>84.8</v>
+        <v>0.4738</v>
       </c>
       <c r="L94">
-        <v>0.4738</v>
-      </c>
-      <c r="M94">
         <v>114.52</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>13189</v>
       </c>
       <c r="B95" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C95" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D95">
         <v>31.5</v>
       </c>
       <c r="E95" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F95">
         <v>74.408920190000003</v>
       </c>
       <c r="G95">
-        <v>940.94</v>
+        <v>9.41</v>
       </c>
       <c r="H95">
-        <v>9.41</v>
-      </c>
-      <c r="I95">
         <v>0.3</v>
       </c>
-      <c r="J95" t="s">
-        <v>14</v>
+      <c r="I95" t="s">
+        <v>13</v>
+      </c>
+      <c r="J95">
+        <v>83.4</v>
       </c>
       <c r="K95">
-        <v>83.4</v>
+        <v>0.45179999999999998</v>
       </c>
       <c r="L95">
-        <v>0.45179999999999998</v>
-      </c>
-      <c r="M95">
         <v>83.33</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>13191</v>
       </c>
       <c r="B96" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C96" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D96">
         <v>31.7</v>
       </c>
       <c r="E96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F96">
         <v>81.178648929999994</v>
       </c>
       <c r="G96">
-        <v>384.81</v>
+        <v>3.85</v>
       </c>
       <c r="H96">
-        <v>3.85</v>
-      </c>
-      <c r="I96">
         <v>0.5</v>
       </c>
-      <c r="J96" t="s">
-        <v>14</v>
+      <c r="I96" t="s">
+        <v>13</v>
+      </c>
+      <c r="J96">
+        <v>85.2</v>
       </c>
       <c r="K96">
-        <v>85.2</v>
+        <v>0.4294</v>
       </c>
       <c r="L96">
-        <v>0.4294</v>
-      </c>
-      <c r="M96">
         <v>32.86</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>13193</v>
       </c>
       <c r="B97" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C97" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D97">
         <v>34.5</v>
       </c>
       <c r="E97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F97">
         <v>73.315701630000007</v>
       </c>
       <c r="G97">
-        <v>489.23</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="H97">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="I97">
         <v>0.4</v>
       </c>
-      <c r="J97" t="s">
-        <v>14</v>
+      <c r="I97" t="s">
+        <v>13</v>
+      </c>
+      <c r="J97">
+        <v>73.599999999999994</v>
       </c>
       <c r="K97">
-        <v>73.599999999999994</v>
+        <v>0.49980000000000002</v>
       </c>
       <c r="L97">
-        <v>0.49980000000000002</v>
-      </c>
-      <c r="M97">
         <v>33.21</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>13195</v>
       </c>
       <c r="B98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C98" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D98">
         <v>33.200000000000003</v>
       </c>
       <c r="E98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F98">
         <v>77.549812320000001</v>
       </c>
       <c r="G98">
-        <v>457.79</v>
+        <v>4.58</v>
       </c>
       <c r="H98">
-        <v>4.58</v>
-      </c>
-      <c r="I98">
         <v>0.2</v>
       </c>
-      <c r="J98" t="s">
-        <v>14</v>
+      <c r="I98" t="s">
+        <v>13</v>
+      </c>
+      <c r="J98">
+        <v>83.2</v>
       </c>
       <c r="K98">
-        <v>83.2</v>
+        <v>0.42049999999999998</v>
       </c>
       <c r="L98">
-        <v>0.42049999999999998</v>
-      </c>
-      <c r="M98">
         <v>103.49</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>13197</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C99" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D99">
         <v>31.2</v>
       </c>
       <c r="E99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F99">
         <v>78.070086799999999</v>
       </c>
       <c r="G99">
-        <v>303.88</v>
+        <v>3.04</v>
       </c>
       <c r="H99">
-        <v>3.04</v>
-      </c>
-      <c r="I99">
         <v>0.2</v>
       </c>
-      <c r="J99" t="s">
-        <v>14</v>
+      <c r="I99" t="s">
+        <v>13</v>
+      </c>
+      <c r="J99">
+        <v>77.8</v>
       </c>
       <c r="K99">
-        <v>77.8</v>
+        <v>0.43440000000000001</v>
       </c>
       <c r="L99">
-        <v>0.43440000000000001</v>
-      </c>
-      <c r="M99">
         <v>23.04</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>13199</v>
       </c>
       <c r="B100" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C100" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D100">
         <v>31.5</v>
       </c>
       <c r="E100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F100">
         <v>73.888022169999999</v>
       </c>
       <c r="G100">
-        <v>802.76</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="H100">
-        <v>8.0299999999999994</v>
-      </c>
-      <c r="I100">
         <v>0.3</v>
       </c>
-      <c r="J100" t="s">
-        <v>14</v>
+      <c r="I100" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100">
+        <v>79.7</v>
       </c>
       <c r="K100">
-        <v>79.7</v>
+        <v>0.46889999999999998</v>
       </c>
       <c r="L100">
-        <v>0.46889999999999998</v>
-      </c>
-      <c r="M100">
         <v>42.11</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>13201</v>
       </c>
       <c r="B101" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C101" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D101">
         <v>28.8</v>
       </c>
       <c r="E101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F101">
         <v>71.892476259999995</v>
       </c>
       <c r="G101">
-        <v>530.54999999999995</v>
+        <v>5.31</v>
       </c>
       <c r="H101">
-        <v>5.31</v>
-      </c>
-      <c r="I101">
         <v>0.4</v>
       </c>
-      <c r="J101" t="s">
-        <v>14</v>
+      <c r="I101" t="s">
+        <v>13</v>
+      </c>
+      <c r="J101">
+        <v>82.6</v>
       </c>
       <c r="K101">
-        <v>82.6</v>
+        <v>0.47320000000000001</v>
       </c>
       <c r="L101">
-        <v>0.47320000000000001</v>
-      </c>
-      <c r="M101">
         <v>20.49</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>13205</v>
       </c>
       <c r="B102" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C102" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D102">
         <v>33.299999999999997</v>
       </c>
       <c r="E102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F102">
         <v>74.323213350000003</v>
       </c>
       <c r="G102">
-        <v>739.32</v>
+        <v>7.39</v>
       </c>
       <c r="H102">
-        <v>7.39</v>
-      </c>
-      <c r="I102">
         <v>0.5</v>
       </c>
-      <c r="J102" t="s">
-        <v>14</v>
+      <c r="I102" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102">
+        <v>77.2</v>
       </c>
       <c r="K102">
-        <v>77.2</v>
+        <v>0.46829999999999999</v>
       </c>
       <c r="L102">
-        <v>0.46829999999999999</v>
-      </c>
-      <c r="M102">
         <v>43.43</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>13207</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C103" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D103">
         <v>31.2</v>
       </c>
       <c r="E103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F103">
         <v>77.034161060000002</v>
       </c>
       <c r="G103">
-        <v>561.15</v>
+        <v>5.61</v>
       </c>
       <c r="H103">
-        <v>5.61</v>
-      </c>
-      <c r="I103">
         <v>0.2</v>
       </c>
-      <c r="J103" t="s">
-        <v>14</v>
+      <c r="I103" t="s">
+        <v>13</v>
+      </c>
+      <c r="J103">
+        <v>85.7</v>
       </c>
       <c r="K103">
-        <v>85.7</v>
+        <v>0.53269999999999995</v>
       </c>
       <c r="L103">
-        <v>0.53269999999999995</v>
-      </c>
-      <c r="M103">
         <v>68.599999999999994</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>13209</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C104" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D104">
         <v>34.5</v>
       </c>
       <c r="E104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F104">
         <v>76.858917000000005</v>
       </c>
       <c r="G104">
-        <v>368.92</v>
+        <v>3.69</v>
       </c>
       <c r="H104">
-        <v>3.69</v>
-      </c>
-      <c r="I104">
         <v>0.2</v>
       </c>
-      <c r="J104" t="s">
-        <v>14</v>
+      <c r="I104" t="s">
+        <v>13</v>
+      </c>
+      <c r="J104">
+        <v>81.7</v>
       </c>
       <c r="K104">
-        <v>81.7</v>
+        <v>0.49909999999999999</v>
       </c>
       <c r="L104">
-        <v>0.49909999999999999</v>
-      </c>
-      <c r="M104">
         <v>37.56</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>13211</v>
       </c>
       <c r="B105" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C105" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D105">
         <v>33</v>
       </c>
       <c r="E105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F105">
         <v>78.043729209999995</v>
       </c>
       <c r="G105">
-        <v>969.63</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="H105">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I105">
         <v>0.2</v>
       </c>
-      <c r="J105" t="s">
-        <v>14</v>
+      <c r="I105" t="s">
+        <v>13</v>
+      </c>
+      <c r="J105">
+        <v>87.7</v>
       </c>
       <c r="K105">
-        <v>87.7</v>
+        <v>0.45169999999999999</v>
       </c>
       <c r="L105">
-        <v>0.45169999999999999</v>
-      </c>
-      <c r="M105">
         <v>53.27</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>13213</v>
       </c>
       <c r="B106" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C106" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D106">
         <v>32.200000000000003</v>
       </c>
       <c r="E106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F106">
         <v>75.466922249999996</v>
       </c>
       <c r="G106">
-        <v>441.06</v>
+        <v>4.41</v>
       </c>
       <c r="H106">
-        <v>4.41</v>
+        <v>0.1</v>
       </c>
       <c r="I106">
-        <v>0.1</v>
+        <v>29.93</v>
       </c>
       <c r="J106">
-        <v>29.93</v>
+        <v>70.7</v>
       </c>
       <c r="K106">
-        <v>70.7</v>
+        <v>0.40960000000000002</v>
       </c>
       <c r="L106">
-        <v>0.40960000000000002</v>
-      </c>
-      <c r="M106">
         <v>115.31</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>13215</v>
       </c>
       <c r="B107" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C107" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D107">
         <v>32.700000000000003</v>
@@ -5360,36 +5038,33 @@
         <v>74.21164958</v>
       </c>
       <c r="G107">
-        <v>650.80999999999995</v>
+        <v>6.51</v>
       </c>
       <c r="H107">
-        <v>6.51</v>
+        <v>0.7</v>
       </c>
       <c r="I107">
-        <v>0.7</v>
+        <v>12.26</v>
       </c>
       <c r="J107">
-        <v>12.26</v>
+        <v>88</v>
       </c>
       <c r="K107">
-        <v>88</v>
+        <v>0.498</v>
       </c>
       <c r="L107">
-        <v>0.498</v>
-      </c>
-      <c r="M107">
         <v>904.19</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A108">
         <v>13217</v>
       </c>
       <c r="B108" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C108" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D108">
         <v>33</v>
@@ -5401,118 +5076,109 @@
         <v>76.690855380000002</v>
       </c>
       <c r="G108">
-        <v>706.11</v>
+        <v>7.06</v>
       </c>
       <c r="H108">
-        <v>7.06</v>
+        <v>0.4</v>
       </c>
       <c r="I108">
-        <v>0.4</v>
+        <v>13.42</v>
       </c>
       <c r="J108">
-        <v>13.42</v>
+        <v>86.6</v>
       </c>
       <c r="K108">
-        <v>86.6</v>
+        <v>0.43880000000000002</v>
       </c>
       <c r="L108">
-        <v>0.43880000000000002</v>
-      </c>
-      <c r="M108">
         <v>394.74</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A109">
         <v>13219</v>
       </c>
       <c r="B109" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C109" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D109">
         <v>28.2</v>
       </c>
       <c r="E109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F109">
         <v>81.222390989999994</v>
       </c>
       <c r="G109">
-        <v>150.6</v>
+        <v>1.51</v>
       </c>
       <c r="H109">
-        <v>1.51</v>
-      </c>
-      <c r="I109">
         <v>0.1</v>
       </c>
-      <c r="J109" t="s">
-        <v>14</v>
+      <c r="I109" t="s">
+        <v>13</v>
+      </c>
+      <c r="J109">
+        <v>94.5</v>
       </c>
       <c r="K109">
-        <v>94.5</v>
+        <v>0.46229999999999999</v>
       </c>
       <c r="L109">
-        <v>0.46229999999999999</v>
-      </c>
-      <c r="M109">
         <v>206.86</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A110">
         <v>13221</v>
       </c>
       <c r="B110" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C110" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D110">
         <v>31.9</v>
       </c>
       <c r="E110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F110">
         <v>77.780519960000007</v>
       </c>
       <c r="G110">
-        <v>448.13</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="H110">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="I110">
         <v>0.1</v>
       </c>
-      <c r="J110" t="s">
-        <v>14</v>
+      <c r="I110" t="s">
+        <v>13</v>
+      </c>
+      <c r="J110">
+        <v>79.7</v>
       </c>
       <c r="K110">
-        <v>79.7</v>
+        <v>0.4158</v>
       </c>
       <c r="L110">
-        <v>0.4158</v>
-      </c>
-      <c r="M110">
         <v>34.01</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A111">
         <v>13223</v>
       </c>
       <c r="B111" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C111" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D111">
         <v>29.1</v>
@@ -5524,200 +5190,185 @@
         <v>78.829475479999999</v>
       </c>
       <c r="G111">
-        <v>164.8</v>
+        <v>1.65</v>
       </c>
       <c r="H111">
-        <v>1.65</v>
+        <v>0.2</v>
       </c>
       <c r="I111">
-        <v>0.2</v>
+        <v>19.57</v>
       </c>
       <c r="J111">
-        <v>19.57</v>
+        <v>89.4</v>
       </c>
       <c r="K111">
-        <v>89.4</v>
+        <v>0.37619999999999998</v>
       </c>
       <c r="L111">
-        <v>0.37619999999999998</v>
-      </c>
-      <c r="M111">
         <v>511.72</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A112">
         <v>13225</v>
       </c>
       <c r="B112" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C112" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D112">
         <v>36.4</v>
       </c>
       <c r="E112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F112">
         <v>73.225547050000003</v>
       </c>
       <c r="G112">
-        <v>353.75</v>
+        <v>3.54</v>
       </c>
       <c r="H112">
-        <v>3.54</v>
-      </c>
-      <c r="I112">
         <v>0.6</v>
       </c>
-      <c r="J112" t="s">
-        <v>14</v>
+      <c r="I112" t="s">
+        <v>13</v>
+      </c>
+      <c r="J112">
+        <v>83</v>
       </c>
       <c r="K112">
-        <v>83</v>
+        <v>0.49759999999999999</v>
       </c>
       <c r="L112">
-        <v>0.49759999999999999</v>
-      </c>
-      <c r="M112">
         <v>180.62</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A113">
         <v>13227</v>
       </c>
       <c r="B113" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D113">
         <v>30.6</v>
       </c>
       <c r="E113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F113">
         <v>77.210143520000003</v>
       </c>
       <c r="G113">
-        <v>305.06</v>
+        <v>3.05</v>
       </c>
       <c r="H113">
-        <v>3.05</v>
-      </c>
-      <c r="I113">
         <v>0.1</v>
       </c>
-      <c r="J113" t="s">
-        <v>14</v>
+      <c r="I113" t="s">
+        <v>13</v>
+      </c>
+      <c r="J113">
+        <v>85.3</v>
       </c>
       <c r="K113">
-        <v>85.3</v>
+        <v>0.4204</v>
       </c>
       <c r="L113">
-        <v>0.4204</v>
-      </c>
-      <c r="M113">
         <v>135.25</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A114">
         <v>13229</v>
       </c>
       <c r="B114" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C114" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D114">
         <v>31.5</v>
       </c>
       <c r="E114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F114">
         <v>76.006781129999993</v>
       </c>
       <c r="G114">
-        <v>455.57</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="H114">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="I114">
         <v>0.1</v>
       </c>
-      <c r="J114" t="s">
-        <v>14</v>
+      <c r="I114" t="s">
+        <v>13</v>
+      </c>
+      <c r="J114">
+        <v>83.4</v>
       </c>
       <c r="K114">
-        <v>83.4</v>
+        <v>0.46820000000000001</v>
       </c>
       <c r="L114">
-        <v>0.46820000000000001</v>
-      </c>
-      <c r="M114">
         <v>56.54</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A115">
         <v>13231</v>
       </c>
       <c r="B115" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C115" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D115">
         <v>29.9</v>
       </c>
       <c r="E115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F115">
         <v>75.930866570000006</v>
       </c>
       <c r="G115">
-        <v>262.29000000000002</v>
+        <v>2.62</v>
       </c>
       <c r="H115">
-        <v>2.62</v>
-      </c>
-      <c r="I115">
         <v>0.1</v>
       </c>
-      <c r="J115" t="s">
-        <v>14</v>
+      <c r="I115" t="s">
+        <v>13</v>
+      </c>
+      <c r="J115">
+        <v>88.2</v>
       </c>
       <c r="K115">
-        <v>88.2</v>
+        <v>0.41970000000000002</v>
       </c>
       <c r="L115">
-        <v>0.41970000000000002</v>
-      </c>
-      <c r="M115">
         <v>84.81</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A116">
         <v>13233</v>
       </c>
       <c r="B116" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C116" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D116">
         <v>35.1</v>
@@ -5729,241 +5380,223 @@
         <v>73.624368349999997</v>
       </c>
       <c r="G116">
-        <v>453.52</v>
+        <v>4.54</v>
       </c>
       <c r="H116">
-        <v>4.54</v>
+        <v>0.2</v>
       </c>
       <c r="I116">
-        <v>0.2</v>
+        <v>32.85</v>
       </c>
       <c r="J116">
-        <v>32.85</v>
+        <v>78.8</v>
       </c>
       <c r="K116">
-        <v>78.8</v>
+        <v>0.4768</v>
       </c>
       <c r="L116">
-        <v>0.4768</v>
-      </c>
-      <c r="M116">
         <v>135.04</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A117">
         <v>13235</v>
       </c>
       <c r="B117" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C117" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D117">
         <v>34.799999999999997</v>
       </c>
       <c r="E117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F117">
         <v>77.544959000000006</v>
       </c>
       <c r="G117">
-        <v>500.13</v>
+        <v>5</v>
       </c>
       <c r="H117">
-        <v>5</v>
-      </c>
-      <c r="I117">
         <v>0.2</v>
       </c>
-      <c r="J117" t="s">
-        <v>14</v>
+      <c r="I117" t="s">
+        <v>13</v>
+      </c>
+      <c r="J117">
+        <v>81.099999999999994</v>
       </c>
       <c r="K117">
-        <v>81.099999999999994</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="L117">
-        <v>0.44600000000000001</v>
-      </c>
-      <c r="M117">
         <v>45</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A118">
         <v>13237</v>
       </c>
       <c r="B118" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C118" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D118">
         <v>31.8</v>
       </c>
       <c r="E118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F118">
         <v>77.647717920000005</v>
       </c>
       <c r="G118">
-        <v>684.8</v>
+        <v>6.85</v>
       </c>
       <c r="H118">
-        <v>6.85</v>
-      </c>
-      <c r="I118">
         <v>0.2</v>
       </c>
-      <c r="J118" t="s">
-        <v>14</v>
+      <c r="I118" t="s">
+        <v>13</v>
+      </c>
+      <c r="J118">
+        <v>87.6</v>
       </c>
       <c r="K118">
-        <v>87.6</v>
+        <v>0.48549999999999999</v>
       </c>
       <c r="L118">
-        <v>0.48549999999999999</v>
-      </c>
-      <c r="M118">
         <v>62.93</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A119">
         <v>13239</v>
       </c>
       <c r="B119" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C119" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D119">
         <v>32.1</v>
       </c>
       <c r="E119" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F119">
         <v>76.248070729999995</v>
       </c>
       <c r="G119">
-        <v>657.61</v>
+        <v>6.58</v>
       </c>
       <c r="H119">
-        <v>6.58</v>
-      </c>
-      <c r="I119">
         <v>0.5</v>
       </c>
-      <c r="J119" t="s">
-        <v>14</v>
+      <c r="I119" t="s">
+        <v>13</v>
+      </c>
+      <c r="J119">
+        <v>64.7</v>
       </c>
       <c r="K119">
-        <v>64.7</v>
+        <v>0.4874</v>
       </c>
       <c r="L119">
-        <v>0.4874</v>
-      </c>
-      <c r="M119">
         <v>15.14</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A120">
         <v>13241</v>
       </c>
       <c r="B120" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C120" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D120">
         <v>28.3</v>
       </c>
       <c r="E120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F120">
         <v>77.061269510000002</v>
       </c>
       <c r="G120">
-        <v>345.13</v>
+        <v>3.45</v>
       </c>
       <c r="H120">
-        <v>3.45</v>
-      </c>
-      <c r="I120">
         <v>0.1</v>
       </c>
-      <c r="J120" t="s">
-        <v>14</v>
+      <c r="I120" t="s">
+        <v>13</v>
+      </c>
+      <c r="J120">
+        <v>84.8</v>
       </c>
       <c r="K120">
-        <v>84.8</v>
+        <v>0.50860000000000005</v>
       </c>
       <c r="L120">
-        <v>0.50860000000000005</v>
-      </c>
-      <c r="M120">
         <v>44.97</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A121">
         <v>13243</v>
       </c>
       <c r="B121" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C121" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D121">
         <v>32</v>
       </c>
       <c r="E121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F121">
         <v>77.20564632</v>
       </c>
       <c r="G121">
-        <v>923.46</v>
+        <v>9.23</v>
       </c>
       <c r="H121">
-        <v>9.23</v>
-      </c>
-      <c r="I121">
         <v>0.7</v>
       </c>
-      <c r="J121" t="s">
-        <v>14</v>
+      <c r="I121" t="s">
+        <v>13</v>
+      </c>
+      <c r="J121">
+        <v>74.5</v>
       </c>
       <c r="K121">
-        <v>74.5</v>
+        <v>0.45</v>
       </c>
       <c r="L121">
-        <v>0.45</v>
-      </c>
-      <c r="M121">
         <v>16.28</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A122">
         <v>13245</v>
       </c>
       <c r="B122" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C122" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D122">
         <v>32.299999999999997</v>
@@ -5975,36 +5608,33 @@
         <v>73.930648540000007</v>
       </c>
       <c r="G122">
-        <v>979.47</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="H122">
-        <v>9.7899999999999991</v>
+        <v>0.9</v>
       </c>
       <c r="I122">
-        <v>0.9</v>
+        <v>15.8</v>
       </c>
       <c r="J122">
-        <v>15.8</v>
+        <v>84.1</v>
       </c>
       <c r="K122">
-        <v>84.1</v>
+        <v>0.4738</v>
       </c>
       <c r="L122">
-        <v>0.4738</v>
-      </c>
-      <c r="M122">
         <v>622.36</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A123">
         <v>13247</v>
       </c>
       <c r="B123" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C123" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D123">
         <v>35.299999999999997</v>
@@ -6016,159 +5646,147 @@
         <v>77.842888110000004</v>
       </c>
       <c r="G123">
-        <v>544.25</v>
+        <v>5.44</v>
       </c>
       <c r="H123">
-        <v>5.44</v>
+        <v>0.5</v>
       </c>
       <c r="I123">
-        <v>0.5</v>
+        <v>11</v>
       </c>
       <c r="J123">
-        <v>11</v>
+        <v>88.8</v>
       </c>
       <c r="K123">
-        <v>88.8</v>
+        <v>0.4229</v>
       </c>
       <c r="L123">
-        <v>0.4229</v>
-      </c>
-      <c r="M123">
         <v>691.1</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A124">
         <v>13249</v>
       </c>
       <c r="B124" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C124" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D124">
         <v>31</v>
       </c>
       <c r="E124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F124">
         <v>79.675681429999997</v>
       </c>
       <c r="G124">
-        <v>288.13</v>
+        <v>2.88</v>
       </c>
       <c r="H124">
-        <v>2.88</v>
-      </c>
-      <c r="I124">
         <v>0.1</v>
       </c>
-      <c r="J124" t="s">
-        <v>14</v>
+      <c r="I124" t="s">
+        <v>13</v>
+      </c>
+      <c r="J124">
+        <v>87.6</v>
       </c>
       <c r="K124">
-        <v>87.6</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="L124">
-        <v>0.44400000000000001</v>
-      </c>
-      <c r="M124">
         <v>31.28</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A125">
         <v>13251</v>
       </c>
       <c r="B125" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C125" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D125">
         <v>31.8</v>
       </c>
       <c r="E125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F125">
         <v>75.513219329999998</v>
       </c>
       <c r="G125">
-        <v>953.33</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="H125">
-        <v>9.5299999999999994</v>
-      </c>
-      <c r="I125">
         <v>0.4</v>
       </c>
-      <c r="J125" t="s">
-        <v>14</v>
+      <c r="I125" t="s">
+        <v>13</v>
+      </c>
+      <c r="J125">
+        <v>83.5</v>
       </c>
       <c r="K125">
-        <v>83.5</v>
+        <v>0.4607</v>
       </c>
       <c r="L125">
-        <v>0.4607</v>
-      </c>
-      <c r="M125">
         <v>21.66</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A126">
         <v>13253</v>
       </c>
       <c r="B126" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C126" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D126">
         <v>32.9</v>
       </c>
       <c r="E126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F126">
         <v>73.883832630000001</v>
       </c>
       <c r="G126">
-        <v>899.43</v>
+        <v>8.99</v>
       </c>
       <c r="H126">
-        <v>8.99</v>
-      </c>
-      <c r="I126">
         <v>0.3</v>
       </c>
-      <c r="J126" t="s">
-        <v>14</v>
+      <c r="I126" t="s">
+        <v>13</v>
+      </c>
+      <c r="J126">
+        <v>86</v>
       </c>
       <c r="K126">
-        <v>86</v>
+        <v>0.60060000000000002</v>
       </c>
       <c r="L126">
-        <v>0.60060000000000002</v>
-      </c>
-      <c r="M126">
         <v>35.03</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A127">
         <v>13255</v>
       </c>
       <c r="B127" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C127" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D127">
         <v>33.799999999999997</v>
@@ -6180,405 +5798,375 @@
         <v>73.800074629999997</v>
       </c>
       <c r="G127">
-        <v>869.55</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="H127">
-        <v>8.6999999999999993</v>
+        <v>0.4</v>
       </c>
       <c r="I127">
-        <v>0.4</v>
+        <v>19.489999999999998</v>
       </c>
       <c r="J127">
-        <v>19.489999999999998</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="K127">
-        <v>81.900000000000006</v>
+        <v>0.4536</v>
       </c>
       <c r="L127">
-        <v>0.4536</v>
-      </c>
-      <c r="M127">
         <v>333.21</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A128">
         <v>13257</v>
       </c>
       <c r="B128" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C128" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D128">
         <v>32.299999999999997</v>
       </c>
       <c r="E128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F128">
         <v>73.46823243</v>
       </c>
       <c r="G128">
-        <v>683.1</v>
+        <v>6.83</v>
       </c>
       <c r="H128">
-        <v>6.83</v>
-      </c>
-      <c r="I128">
         <v>0.2</v>
       </c>
-      <c r="J128" t="s">
-        <v>14</v>
+      <c r="I128" t="s">
+        <v>13</v>
+      </c>
+      <c r="J128">
+        <v>82.1</v>
       </c>
       <c r="K128">
-        <v>82.1</v>
+        <v>0.45250000000000001</v>
       </c>
       <c r="L128">
-        <v>0.45250000000000001</v>
-      </c>
-      <c r="M128">
         <v>143.72999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A129">
         <v>13259</v>
       </c>
       <c r="B129" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C129" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D129">
         <v>32.799999999999997</v>
       </c>
       <c r="E129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F129">
         <v>76.566811369999996</v>
       </c>
       <c r="G129">
-        <v>640.80999999999995</v>
+        <v>6.41</v>
       </c>
       <c r="H129">
-        <v>6.41</v>
-      </c>
-      <c r="I129">
         <v>1.2</v>
       </c>
-      <c r="J129" t="s">
-        <v>14</v>
+      <c r="I129" t="s">
+        <v>13</v>
+      </c>
+      <c r="J129">
+        <v>68.099999999999994</v>
       </c>
       <c r="K129">
-        <v>68.099999999999994</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="L129">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="M129">
         <v>13.72</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A130">
         <v>13261</v>
       </c>
       <c r="B130" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C130" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D130">
         <v>33.1</v>
       </c>
       <c r="E130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F130">
         <v>73.112161630000003</v>
       </c>
       <c r="G130">
-        <v>674.6</v>
+        <v>6.75</v>
       </c>
       <c r="H130">
-        <v>6.75</v>
-      </c>
-      <c r="I130">
         <v>0.5</v>
       </c>
-      <c r="J130" t="s">
-        <v>14</v>
+      <c r="I130" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130">
+        <v>81.400000000000006</v>
       </c>
       <c r="K130">
-        <v>81.400000000000006</v>
+        <v>0.47510000000000002</v>
       </c>
       <c r="L130">
-        <v>0.47510000000000002</v>
-      </c>
-      <c r="M130">
         <v>62.26</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A131">
         <v>13263</v>
       </c>
       <c r="B131" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C131" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D131">
         <v>33.9</v>
       </c>
       <c r="E131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F131">
         <v>76.584613230000002</v>
       </c>
       <c r="G131">
-        <v>678.49</v>
+        <v>6.78</v>
       </c>
       <c r="H131">
-        <v>6.78</v>
-      </c>
-      <c r="I131">
         <v>0.4</v>
       </c>
-      <c r="J131" t="s">
-        <v>14</v>
+      <c r="I131" t="s">
+        <v>13</v>
+      </c>
+      <c r="J131">
+        <v>82.3</v>
       </c>
       <c r="K131">
-        <v>82.3</v>
+        <v>0.44109999999999999</v>
       </c>
       <c r="L131">
-        <v>0.44109999999999999</v>
-      </c>
-      <c r="M131">
         <v>16.149999999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A132">
         <v>13265</v>
       </c>
       <c r="B132" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C132" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D132">
         <v>31.8</v>
       </c>
       <c r="E132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G132">
-        <v>1217.29</v>
+        <v>12.17</v>
       </c>
       <c r="H132">
-        <v>12.17</v>
-      </c>
-      <c r="I132">
         <v>0.4</v>
       </c>
-      <c r="J132" t="s">
-        <v>14</v>
+      <c r="I132" t="s">
+        <v>13</v>
+      </c>
+      <c r="J132">
+        <v>71</v>
       </c>
       <c r="K132">
-        <v>71</v>
+        <v>0.45569999999999999</v>
       </c>
       <c r="L132">
-        <v>0.45569999999999999</v>
-      </c>
-      <c r="M132">
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A133">
         <v>13267</v>
       </c>
       <c r="B133" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C133" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D133">
         <v>34.9</v>
       </c>
       <c r="E133" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F133">
         <v>73.945492659999999</v>
       </c>
       <c r="G133">
-        <v>752.26</v>
+        <v>7.52</v>
       </c>
       <c r="H133">
-        <v>7.52</v>
-      </c>
-      <c r="I133">
         <v>0.4</v>
       </c>
-      <c r="J133" t="s">
-        <v>14</v>
+      <c r="I133" t="s">
+        <v>13</v>
+      </c>
+      <c r="J133">
+        <v>75.8</v>
       </c>
       <c r="K133">
-        <v>75.8</v>
+        <v>0.45429999999999998</v>
       </c>
       <c r="L133">
-        <v>0.45429999999999998</v>
-      </c>
-      <c r="M133">
         <v>52.79</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A134">
         <v>13269</v>
       </c>
       <c r="B134" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C134" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D134">
         <v>32</v>
       </c>
       <c r="E134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F134">
         <v>75.90543916</v>
       </c>
       <c r="G134">
-        <v>812.61</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="H134">
-        <v>8.1300000000000008</v>
-      </c>
-      <c r="I134">
         <v>0.5</v>
       </c>
-      <c r="J134" t="s">
-        <v>14</v>
+      <c r="I134" t="s">
+        <v>13</v>
+      </c>
+      <c r="J134">
+        <v>78.5</v>
       </c>
       <c r="K134">
-        <v>78.5</v>
+        <v>0.4839</v>
       </c>
       <c r="L134">
-        <v>0.4839</v>
-      </c>
-      <c r="M134">
         <v>21.55</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A135">
         <v>13271</v>
       </c>
       <c r="B135" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C135" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D135">
         <v>29.4</v>
       </c>
       <c r="E135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F135">
         <v>79.152562639999999</v>
       </c>
       <c r="G135">
-        <v>596.14</v>
+        <v>5.96</v>
       </c>
       <c r="H135">
-        <v>5.96</v>
-      </c>
-      <c r="I135">
         <v>0.6</v>
       </c>
-      <c r="J135" t="s">
-        <v>14</v>
+      <c r="I135" t="s">
+        <v>13</v>
+      </c>
+      <c r="J135">
+        <v>70.3</v>
       </c>
       <c r="K135">
-        <v>70.3</v>
+        <v>0.4803</v>
       </c>
       <c r="L135">
-        <v>0.4803</v>
-      </c>
-      <c r="M135">
         <v>36.67</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A136">
         <v>13273</v>
       </c>
       <c r="B136" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C136" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D136">
         <v>32.200000000000003</v>
       </c>
       <c r="E136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F136">
         <v>75.057023830000006</v>
       </c>
       <c r="G136">
-        <v>1009.2</v>
+        <v>10.09</v>
       </c>
       <c r="H136">
-        <v>10.09</v>
-      </c>
-      <c r="I136">
         <v>0.6</v>
       </c>
-      <c r="J136" t="s">
-        <v>14</v>
+      <c r="I136" t="s">
+        <v>13</v>
+      </c>
+      <c r="J136">
+        <v>77.5</v>
       </c>
       <c r="K136">
-        <v>77.5</v>
+        <v>0.47089999999999999</v>
       </c>
       <c r="L136">
-        <v>0.47089999999999999</v>
-      </c>
-      <c r="M136">
         <v>26.02</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A137">
         <v>13275</v>
       </c>
       <c r="B137" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C137" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D137">
         <v>32.6</v>
@@ -6590,36 +6178,33 @@
         <v>75.841071880000001</v>
       </c>
       <c r="G137">
-        <v>540.03</v>
+        <v>5.4</v>
       </c>
       <c r="H137">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="I137">
-        <v>0.5</v>
+        <v>29.25</v>
       </c>
       <c r="J137">
-        <v>29.25</v>
+        <v>84.9</v>
       </c>
       <c r="K137">
-        <v>84.9</v>
+        <v>0.50009999999999999</v>
       </c>
       <c r="L137">
-        <v>0.50009999999999999</v>
-      </c>
-      <c r="M137">
         <v>81.95</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A138">
         <v>13277</v>
       </c>
       <c r="B138" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C138" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D138">
         <v>31.9</v>
@@ -6631,36 +6216,33 @@
         <v>75.445422429999994</v>
       </c>
       <c r="G138">
-        <v>920.17</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H138">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="I138">
         <v>0.5</v>
       </c>
-      <c r="J138" t="s">
-        <v>14</v>
+      <c r="I138" t="s">
+        <v>13</v>
+      </c>
+      <c r="J138">
+        <v>81.900000000000006</v>
       </c>
       <c r="K138">
-        <v>81.900000000000006</v>
+        <v>0.45710000000000001</v>
       </c>
       <c r="L138">
-        <v>0.45710000000000001</v>
-      </c>
-      <c r="M138">
         <v>155.4</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A139">
         <v>13279</v>
       </c>
       <c r="B139" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C139" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D139">
         <v>36.9</v>
@@ -6672,118 +6254,109 @@
         <v>73.353354420000002</v>
       </c>
       <c r="G139">
-        <v>1299.27</v>
+        <v>12.99</v>
       </c>
       <c r="H139">
-        <v>12.99</v>
-      </c>
-      <c r="I139">
         <v>0.4</v>
       </c>
-      <c r="J139" t="s">
-        <v>14</v>
+      <c r="I139" t="s">
+        <v>13</v>
+      </c>
+      <c r="J139">
+        <v>80.099999999999994</v>
       </c>
       <c r="K139">
-        <v>80.099999999999994</v>
+        <v>0.53959999999999997</v>
       </c>
       <c r="L139">
-        <v>0.53959999999999997</v>
-      </c>
-      <c r="M139">
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A140">
         <v>13281</v>
       </c>
       <c r="B140" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C140" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D140">
         <v>29.3</v>
       </c>
       <c r="E140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F140">
         <v>76.53351499</v>
       </c>
       <c r="G140">
-        <v>428.3</v>
+        <v>4.28</v>
       </c>
       <c r="H140">
-        <v>4.28</v>
-      </c>
-      <c r="I140">
         <v>0.1</v>
       </c>
-      <c r="J140" t="s">
-        <v>14</v>
+      <c r="I140" t="s">
+        <v>13</v>
+      </c>
+      <c r="J140">
+        <v>89.9</v>
       </c>
       <c r="K140">
-        <v>89.9</v>
+        <v>0.44369999999999998</v>
       </c>
       <c r="L140">
-        <v>0.44369999999999998</v>
-      </c>
-      <c r="M140">
         <v>69.790000000000006</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A141">
         <v>13283</v>
       </c>
       <c r="B141" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C141" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D141">
         <v>31.4</v>
       </c>
       <c r="E141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F141">
         <v>76.077870669999996</v>
       </c>
       <c r="G141">
-        <v>1264.52</v>
+        <v>12.65</v>
       </c>
       <c r="H141">
-        <v>12.65</v>
-      </c>
-      <c r="I141">
         <v>0.4</v>
       </c>
-      <c r="J141" t="s">
-        <v>14</v>
+      <c r="I141" t="s">
+        <v>13</v>
+      </c>
+      <c r="J141">
+        <v>73.7</v>
       </c>
       <c r="K141">
-        <v>73.7</v>
+        <v>0.52549999999999997</v>
       </c>
       <c r="L141">
-        <v>0.52549999999999997</v>
-      </c>
-      <c r="M141">
         <v>34.07</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A142">
         <v>13285</v>
       </c>
       <c r="B142" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C142" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D142">
         <v>31.7</v>
@@ -6795,200 +6368,185 @@
         <v>75.327121050000002</v>
       </c>
       <c r="G142">
-        <v>869.34</v>
+        <v>8.69</v>
       </c>
       <c r="H142">
-        <v>8.69</v>
-      </c>
-      <c r="I142">
         <v>0.3</v>
       </c>
-      <c r="J142" t="s">
-        <v>14</v>
+      <c r="I142" t="s">
+        <v>13</v>
+      </c>
+      <c r="J142">
+        <v>83.4</v>
       </c>
       <c r="K142">
-        <v>83.4</v>
+        <v>0.47149999999999997</v>
       </c>
       <c r="L142">
-        <v>0.47149999999999997</v>
-      </c>
-      <c r="M142">
         <v>168.88</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A143">
         <v>13287</v>
       </c>
       <c r="B143" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C143" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D143">
         <v>33.1</v>
       </c>
       <c r="E143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F143">
         <v>73.114348430000007</v>
       </c>
       <c r="G143">
-        <v>965.03</v>
+        <v>9.65</v>
       </c>
       <c r="H143">
-        <v>9.65</v>
-      </c>
-      <c r="I143">
         <v>0.7</v>
       </c>
-      <c r="J143" t="s">
-        <v>14</v>
+      <c r="I143" t="s">
+        <v>13</v>
+      </c>
+      <c r="J143">
+        <v>81.2</v>
       </c>
       <c r="K143">
-        <v>81.2</v>
+        <v>0.47610000000000002</v>
       </c>
       <c r="L143">
-        <v>0.47610000000000002</v>
-      </c>
-      <c r="M143">
         <v>27.83</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A144">
         <v>13289</v>
       </c>
       <c r="B144" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C144" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D144">
         <v>34.700000000000003</v>
       </c>
       <c r="E144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F144">
         <v>72.575174989999994</v>
       </c>
       <c r="G144">
-        <v>743.23</v>
+        <v>7.43</v>
       </c>
       <c r="H144">
-        <v>7.43</v>
-      </c>
-      <c r="I144">
         <v>0.2</v>
       </c>
-      <c r="J144" t="s">
-        <v>14</v>
+      <c r="I144" t="s">
+        <v>13</v>
+      </c>
+      <c r="J144">
+        <v>74.2</v>
       </c>
       <c r="K144">
-        <v>74.2</v>
+        <v>0.47870000000000001</v>
       </c>
       <c r="L144">
-        <v>0.47870000000000001</v>
-      </c>
-      <c r="M144">
         <v>22.91</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A145">
         <v>13291</v>
       </c>
       <c r="B145" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C145" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D145">
         <v>29.4</v>
       </c>
       <c r="E145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F145">
         <v>78.598418199999998</v>
       </c>
       <c r="G145">
-        <v>399.69</v>
+        <v>4</v>
       </c>
       <c r="H145">
-        <v>4</v>
-      </c>
-      <c r="I145">
         <v>0.2</v>
       </c>
-      <c r="J145" t="s">
-        <v>14</v>
+      <c r="I145" t="s">
+        <v>13</v>
+      </c>
+      <c r="J145">
+        <v>89</v>
       </c>
       <c r="K145">
-        <v>89</v>
+        <v>0.46850000000000003</v>
       </c>
       <c r="L145">
-        <v>0.46850000000000003</v>
-      </c>
-      <c r="M145">
         <v>72.3</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A146">
         <v>13293</v>
       </c>
       <c r="B146" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C146" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D146">
         <v>31.5</v>
       </c>
       <c r="E146" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F146">
         <v>74.162644689999993</v>
       </c>
       <c r="G146">
-        <v>640.22</v>
+        <v>6.4</v>
       </c>
       <c r="H146">
-        <v>6.4</v>
-      </c>
-      <c r="I146">
         <v>0.3</v>
       </c>
-      <c r="J146" t="s">
-        <v>14</v>
+      <c r="I146" t="s">
+        <v>13</v>
+      </c>
+      <c r="J146">
+        <v>82.3</v>
       </c>
       <c r="K146">
-        <v>82.3</v>
+        <v>0.4773</v>
       </c>
       <c r="L146">
-        <v>0.4773</v>
-      </c>
-      <c r="M146">
         <v>81.11</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A147">
         <v>13295</v>
       </c>
       <c r="B147" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C147" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D147">
         <v>32.6</v>
@@ -7000,36 +6558,33 @@
         <v>74.584073480000001</v>
       </c>
       <c r="G147">
-        <v>671.02</v>
+        <v>6.71</v>
       </c>
       <c r="H147">
-        <v>6.71</v>
+        <v>0.2</v>
       </c>
       <c r="I147">
-        <v>0.2</v>
+        <v>18.64</v>
       </c>
       <c r="J147">
-        <v>18.64</v>
+        <v>82</v>
       </c>
       <c r="K147">
-        <v>82</v>
+        <v>0.45</v>
       </c>
       <c r="L147">
-        <v>0.45</v>
-      </c>
-      <c r="M147">
         <v>154.66</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A148">
         <v>13297</v>
       </c>
       <c r="B148" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C148" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D148">
         <v>31.4</v>
@@ -7041,36 +6596,33 @@
         <v>76.867012939999995</v>
       </c>
       <c r="G148">
-        <v>645.1</v>
+        <v>6.45</v>
       </c>
       <c r="H148">
-        <v>6.45</v>
+        <v>0.3</v>
       </c>
       <c r="I148">
-        <v>0.3</v>
+        <v>20.09</v>
       </c>
       <c r="J148">
-        <v>20.09</v>
+        <v>86.9</v>
       </c>
       <c r="K148">
-        <v>86.9</v>
+        <v>0.42209999999999998</v>
       </c>
       <c r="L148">
-        <v>0.42209999999999998</v>
-      </c>
-      <c r="M148">
         <v>279.8</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A149">
         <v>13299</v>
       </c>
       <c r="B149" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C149" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D149">
         <v>34</v>
@@ -7082,282 +6634,261 @@
         <v>74.198865159999997</v>
       </c>
       <c r="G149">
-        <v>992.68</v>
+        <v>9.93</v>
       </c>
       <c r="H149">
-        <v>9.93</v>
-      </c>
-      <c r="I149">
         <v>0.6</v>
       </c>
-      <c r="J149" t="s">
-        <v>14</v>
+      <c r="I149" t="s">
+        <v>13</v>
+      </c>
+      <c r="J149">
+        <v>81.400000000000006</v>
       </c>
       <c r="K149">
-        <v>81.400000000000006</v>
+        <v>0.4652</v>
       </c>
       <c r="L149">
-        <v>0.4652</v>
-      </c>
-      <c r="M149">
         <v>39.58</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A150">
         <v>13301</v>
       </c>
       <c r="B150" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C150" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D150">
         <v>33.700000000000003</v>
       </c>
       <c r="E150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F150">
         <v>71.8341767</v>
       </c>
       <c r="G150">
-        <v>725.31</v>
+        <v>7.25</v>
       </c>
       <c r="H150">
-        <v>7.25</v>
-      </c>
-      <c r="I150">
         <v>0.5</v>
       </c>
-      <c r="J150" t="s">
-        <v>14</v>
+      <c r="I150" t="s">
+        <v>13</v>
+      </c>
+      <c r="J150">
+        <v>73.2</v>
       </c>
       <c r="K150">
-        <v>73.2</v>
+        <v>0.5202</v>
       </c>
       <c r="L150">
-        <v>0.5202</v>
-      </c>
-      <c r="M150">
         <v>18.63</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A151">
         <v>13303</v>
       </c>
       <c r="B151" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C151" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D151">
         <v>32.5</v>
       </c>
       <c r="E151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F151">
         <v>75.792054750000005</v>
       </c>
       <c r="G151">
-        <v>940.39</v>
+        <v>9.4</v>
       </c>
       <c r="H151">
-        <v>9.4</v>
-      </c>
-      <c r="I151">
         <v>0.3</v>
       </c>
-      <c r="J151" t="s">
-        <v>14</v>
+      <c r="I151" t="s">
+        <v>13</v>
+      </c>
+      <c r="J151">
+        <v>81.3</v>
       </c>
       <c r="K151">
-        <v>81.3</v>
+        <v>0.45929999999999999</v>
       </c>
       <c r="L151">
-        <v>0.45929999999999999</v>
-      </c>
-      <c r="M151">
         <v>30.12</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A152">
         <v>13305</v>
       </c>
       <c r="B152" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C152" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D152">
         <v>34.9</v>
       </c>
       <c r="E152" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F152">
         <v>73.733513529999996</v>
       </c>
       <c r="G152">
-        <v>577.79999999999995</v>
+        <v>5.78</v>
       </c>
       <c r="H152">
-        <v>5.78</v>
-      </c>
-      <c r="I152">
         <v>0.4</v>
       </c>
-      <c r="J152" t="s">
-        <v>14</v>
+      <c r="I152" t="s">
+        <v>13</v>
+      </c>
+      <c r="J152">
+        <v>83.4</v>
       </c>
       <c r="K152">
-        <v>83.4</v>
+        <v>0.4345</v>
       </c>
       <c r="L152">
-        <v>0.4345</v>
-      </c>
-      <c r="M152">
         <v>46.4</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A153">
         <v>13307</v>
       </c>
       <c r="B153" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C153" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D153">
         <v>31.7</v>
       </c>
       <c r="E153" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F153">
         <v>81.511879260000001</v>
       </c>
       <c r="G153">
-        <v>190.04</v>
-      </c>
-      <c r="H153">
         <v>1.9</v>
       </c>
+      <c r="H153" t="s">
+        <v>13</v>
+      </c>
       <c r="I153" t="s">
-        <v>14</v>
-      </c>
-      <c r="J153" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="J153">
+        <v>79.3</v>
       </c>
       <c r="K153">
-        <v>79.3</v>
+        <v>0.49519999999999997</v>
       </c>
       <c r="L153">
-        <v>0.49519999999999997</v>
-      </c>
-      <c r="M153">
         <v>12.47</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A154">
         <v>13309</v>
       </c>
       <c r="B154" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C154" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D154">
         <v>29.6</v>
       </c>
       <c r="E154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F154">
         <v>78.937564140000006</v>
       </c>
       <c r="G154">
-        <v>278.58999999999997</v>
+        <v>2.79</v>
       </c>
       <c r="H154">
-        <v>2.79</v>
-      </c>
-      <c r="I154">
         <v>0.4</v>
       </c>
-      <c r="J154" t="s">
-        <v>14</v>
+      <c r="I154" t="s">
+        <v>13</v>
+      </c>
+      <c r="J154">
+        <v>80.8</v>
       </c>
       <c r="K154">
-        <v>80.8</v>
+        <v>0.44519999999999998</v>
       </c>
       <c r="L154">
-        <v>0.44519999999999998</v>
-      </c>
-      <c r="M154">
         <v>26.83</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A155">
         <v>13311</v>
       </c>
       <c r="B155" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C155" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D155">
         <v>28.3</v>
       </c>
       <c r="E155" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F155">
         <v>78.967479429999997</v>
       </c>
       <c r="G155">
-        <v>401.78</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="H155">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="I155">
         <v>0.1</v>
       </c>
-      <c r="J155" t="s">
-        <v>14</v>
+      <c r="I155" t="s">
+        <v>13</v>
+      </c>
+      <c r="J155">
+        <v>85.2</v>
       </c>
       <c r="K155">
-        <v>85.2</v>
+        <v>0.4204</v>
       </c>
       <c r="L155">
-        <v>0.4204</v>
-      </c>
-      <c r="M155">
         <v>122.49</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A156">
         <v>13313</v>
       </c>
       <c r="B156" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C156" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D156">
         <v>35.200000000000003</v>
@@ -7369,194 +6900,179 @@
         <v>77.955500610000001</v>
       </c>
       <c r="G156">
-        <v>602.83000000000004</v>
+        <v>6.03</v>
       </c>
       <c r="H156">
-        <v>6.03</v>
+        <v>0.2</v>
       </c>
       <c r="I156">
-        <v>0.2</v>
+        <v>13.38</v>
       </c>
       <c r="J156">
-        <v>13.38</v>
+        <v>69.5</v>
       </c>
       <c r="K156">
-        <v>69.5</v>
+        <v>0.45850000000000002</v>
       </c>
       <c r="L156">
-        <v>0.45850000000000002</v>
-      </c>
-      <c r="M156">
         <v>358.9</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A157">
         <v>13315</v>
       </c>
       <c r="B157" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C157" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D157">
         <v>31.9</v>
       </c>
       <c r="E157" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F157">
         <v>74.968608840000002</v>
       </c>
       <c r="G157">
-        <v>505.73</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="H157">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="I157">
         <v>0.7</v>
       </c>
-      <c r="J157" t="s">
-        <v>14</v>
+      <c r="I157" t="s">
+        <v>13</v>
+      </c>
+      <c r="J157">
+        <v>82.1</v>
       </c>
       <c r="K157">
-        <v>82.1</v>
+        <v>0.46789999999999998</v>
       </c>
       <c r="L157">
-        <v>0.46789999999999998</v>
-      </c>
-      <c r="M157">
         <v>23.36</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A158">
         <v>13317</v>
       </c>
       <c r="B158" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C158" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D158">
         <v>32</v>
       </c>
       <c r="E158" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F158">
         <v>74.43326759</v>
       </c>
       <c r="G158">
-        <v>746.8</v>
+        <v>7.47</v>
       </c>
       <c r="H158">
-        <v>7.47</v>
-      </c>
-      <c r="I158">
         <v>0.3</v>
       </c>
-      <c r="J158" t="s">
-        <v>14</v>
+      <c r="I158" t="s">
+        <v>13</v>
+      </c>
+      <c r="J158">
+        <v>83.7</v>
       </c>
       <c r="K158">
-        <v>83.7</v>
+        <v>0.50819999999999999</v>
       </c>
       <c r="L158">
-        <v>0.50819999999999999</v>
-      </c>
-      <c r="M158">
         <v>20.97</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A159">
         <v>13319</v>
       </c>
       <c r="B159" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C159" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D159">
         <v>35.5</v>
       </c>
       <c r="E159" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F159">
         <v>73.797583799999998</v>
       </c>
       <c r="G159">
-        <v>550.66</v>
+        <v>5.51</v>
       </c>
       <c r="H159">
-        <v>5.51</v>
-      </c>
-      <c r="I159">
         <v>0.2</v>
       </c>
-      <c r="J159" t="s">
-        <v>14</v>
+      <c r="I159" t="s">
+        <v>13</v>
+      </c>
+      <c r="J159">
+        <v>84.4</v>
       </c>
       <c r="K159">
-        <v>84.4</v>
+        <v>0.48380000000000001</v>
       </c>
       <c r="L159">
-        <v>0.48380000000000001</v>
-      </c>
-      <c r="M159">
         <v>20.059999999999999</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A160">
         <v>13321</v>
       </c>
       <c r="B160" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C160" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D160">
         <v>35.200000000000003</v>
       </c>
       <c r="E160" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F160">
         <v>76.060355729999998</v>
       </c>
       <c r="G160">
-        <v>680.99</v>
+        <v>6.81</v>
       </c>
       <c r="H160">
-        <v>6.81</v>
+        <v>0.4</v>
       </c>
       <c r="I160">
-        <v>0.4</v>
+        <v>54.33</v>
       </c>
       <c r="J160">
-        <v>54.33</v>
+        <v>82.9</v>
       </c>
       <c r="K160">
-        <v>82.9</v>
+        <v>0.45660000000000001</v>
       </c>
       <c r="L160">
-        <v>0.45660000000000001</v>
-      </c>
-      <c r="M160">
         <v>35.909999999999997</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M160">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L160">
     <sortCondition ref="C1:C160"/>
   </sortState>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
